--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118981652</v>
+        <v>118981709</v>
       </c>
       <c r="B2" t="n">
-        <v>97874</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
@@ -775,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 7 st skott/stjälkar. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxta bålar av garnlav. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,6 +779,31 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Döda grenar på levande träd. # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,7 +821,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118981029</v>
+        <v>118981456</v>
       </c>
       <c r="B3" t="n">
         <v>97874</v>
@@ -848,7 +856,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,7 +866,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -873,10 +881,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499309</v>
+        <v>499272</v>
       </c>
       <c r="R3" t="n">
-        <v>7017233</v>
+        <v>7017240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,7 +921,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 19 st skott/stjälkar inom ca 5 m2 yta. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Spindelblomster med minst 7 st skott/stjälkar inom ca 3 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -951,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118981456</v>
+        <v>118981133</v>
       </c>
       <c r="B4" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,30 +971,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -996,7 +1004,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1011,10 +1019,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499272</v>
+        <v>499309</v>
       </c>
       <c r="R4" t="n">
-        <v>7017240</v>
+        <v>7017233</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1051,7 +1059,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 7 st skott/stjälkar inom ca 3 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 57 st skott/stjälkar och 4 st överblommade blomstänglar inom ca 5 m2 yta. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,7 +1097,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118980671</v>
+        <v>118981571</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1124,7 +1132,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1134,7 +1142,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1149,10 +1157,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499374</v>
+        <v>499264</v>
       </c>
       <c r="R5" t="n">
-        <v>7017134</v>
+        <v>7017222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1189,7 +1197,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Knärot med minst 9 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,7 +1217,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1227,10 +1235,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118981871</v>
+        <v>118980813</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>97874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,30 +1247,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1287,13 +1295,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499309</v>
+        <v>499374</v>
       </c>
       <c r="R6" t="n">
-        <v>7017130</v>
+        <v>7017134</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1327,7 +1335,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar, 1 st överblommad blomstängel och 1 st vinterståndare inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Spindelblomster med minst 2 st skott/stjälkar inom ca 1 m2 yta. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,7 +1355,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns liggande och stående död ved. På frisk mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1365,7 +1373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118980813</v>
+        <v>118982021</v>
       </c>
       <c r="B7" t="n">
         <v>97874</v>
@@ -1400,7 +1408,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1410,7 +1418,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1425,10 +1433,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499374</v>
+        <v>499371</v>
       </c>
       <c r="R7" t="n">
-        <v>7017134</v>
+        <v>7017042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1465,7 +1473,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 2 st skott/stjälkar inom ca 1 m2 yta. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Spindelblomster med minst 16 st skott/stjälkar inom 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,7 +1493,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1503,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118981709</v>
+        <v>118980671</v>
       </c>
       <c r="B8" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1515,41 +1523,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499264</v>
+        <v>499374</v>
       </c>
       <c r="R8" t="n">
-        <v>7017222</v>
+        <v>7017134</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1586,7 +1611,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar av garnlav. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 9 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1606,32 +1631,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Döda grenar på levande träd. # Picea abies # Flera granar.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118981571</v>
+        <v>118980864</v>
       </c>
       <c r="B9" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1661,58 +1661,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499264</v>
+        <v>499374</v>
       </c>
       <c r="R9" t="n">
-        <v>7017222</v>
+        <v>7017134</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1749,7 +1732,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ett par bålar av garnlav i äldre granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1769,7 +1752,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Död gren på lenande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1787,10 +1790,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118981133</v>
+        <v>118981029</v>
       </c>
       <c r="B10" t="n">
-        <v>97853</v>
+        <v>97874</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1799,30 +1802,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1887,7 +1890,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Knärot med minst 57 st skott/stjälkar och 4 st överblommade blomstänglar inom ca 5 m2 yta. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Spindelblomster med minst 19 st skott/stjälkar inom ca 5 m2 yta. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1925,10 +1928,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118982021</v>
+        <v>118981871</v>
       </c>
       <c r="B11" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1937,30 +1940,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1970,7 +1973,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1985,13 +1988,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499371</v>
+        <v>499309</v>
       </c>
       <c r="R11" t="n">
-        <v>7017042</v>
+        <v>7017130</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2025,7 +2028,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 16 st skott/stjälkar inom 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar, 1 st överblommad blomstängel och 1 st vinterståndare inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2045,7 +2048,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2063,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118980864</v>
+        <v>118981652</v>
       </c>
       <c r="B12" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2075,41 +2078,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499374</v>
+        <v>499264</v>
       </c>
       <c r="R12" t="n">
-        <v>7017134</v>
+        <v>7017222</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2146,7 +2166,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett par bålar av garnlav i äldre granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Spindelblomster med minst 7 st skott/stjälkar. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,27 +2186,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Död gren på lenande träd. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2202,6 +2202,3643 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120278324</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90558</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499536</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7016886</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120278443</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499314</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7016944</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120277899</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>499598</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7016864</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120277408</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90558</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>499566</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7016949</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120275534</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>499369</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7016923</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120276443</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>499460</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7016990</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120276314</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>499419</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7016971</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120273132</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>499362</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7017047</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120272977</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>499347</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7017018</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120277714</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>499640</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7016917</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120274378</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>499337</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7017015</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120275293</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>499319</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7016956</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120277525</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>499634</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7016955</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120275167</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499357</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7016976</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120276615</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>499484</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7016963</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120272547</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>499399</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7017051</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120273861</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>499335</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7017016</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120275779</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>499408</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7016909</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120277809</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>499618</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7016885</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120278049</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>499546</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7016839</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120275394</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>499319</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7016956</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120273613</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>499334</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7017033</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120277582</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96862</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>499634</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7016955</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120272665</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>499381</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7017041</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120273384</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>499362</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7017033</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120276956</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>499543</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7016946</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120272977</v>
+        <v>120277714</v>
       </c>
       <c r="B21" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3354,53 +3354,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499347</v>
+        <v>499640</v>
       </c>
       <c r="R21" t="n">
-        <v>7017018</v>
+        <v>7016917</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3434,7 +3421,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3443,6 +3430,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3453,7 +3441,27 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3471,10 +3479,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120277714</v>
+        <v>120272977</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3487,40 +3495,53 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499640</v>
+        <v>499347</v>
       </c>
       <c r="R22" t="n">
-        <v>7016917</v>
+        <v>7017018</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3554,7 +3575,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3563,7 +3584,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3574,27 +3594,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -5839,6 +5839,293 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120279007</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90558</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>499409</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7017042</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120278994</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>499337</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7017015</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -3761,7 +3761,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275293</v>
+        <v>120275167</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499319</v>
+        <v>499357</v>
       </c>
       <c r="R24" t="n">
-        <v>7016956</v>
+        <v>7016976</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120277525</v>
+        <v>120275293</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3959,13 +3959,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499634</v>
+        <v>499319</v>
       </c>
       <c r="R25" t="n">
-        <v>7016955</v>
+        <v>7016956</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120275167</v>
+        <v>120276615</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499357</v>
+        <v>499484</v>
       </c>
       <c r="R26" t="n">
-        <v>7016976</v>
+        <v>7016963</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4175,7 +4175,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120276615</v>
+        <v>120277525</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -4235,13 +4235,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499484</v>
+        <v>499634</v>
       </c>
       <c r="R27" t="n">
-        <v>7016963</v>
+        <v>7016955</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278324</v>
+        <v>120277582</v>
       </c>
       <c r="B13" t="n">
-        <v>90558</v>
+        <v>96885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,49 +2216,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499536</v>
+        <v>499634</v>
       </c>
       <c r="R13" t="n">
-        <v>7016886</v>
+        <v>7016955</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2295,7 +2300,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2315,22 +2320,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2348,10 +2338,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278443</v>
+        <v>120277408</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>90576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2364,53 +2354,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499314</v>
+        <v>499566</v>
       </c>
       <c r="R14" t="n">
-        <v>7016944</v>
+        <v>7016949</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2444,7 +2429,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2453,6 +2438,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2463,7 +2449,27 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2481,10 +2487,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120277899</v>
+        <v>120277714</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2493,58 +2499,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499598</v>
+        <v>499640</v>
       </c>
       <c r="R15" t="n">
-        <v>7016864</v>
+        <v>7016917</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2581,7 +2570,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2602,6 +2591,26 @@
       <c r="AI15" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2619,10 +2628,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120277408</v>
+        <v>120273861</v>
       </c>
       <c r="B16" t="n">
-        <v>90558</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2631,52 +2640,61 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499566</v>
+        <v>499335</v>
       </c>
       <c r="R16" t="n">
-        <v>7016949</v>
+        <v>7017016</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2710,7 +2728,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2730,27 +2748,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2768,10 +2766,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120275534</v>
+        <v>120275394</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2801,11 +2799,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2815,13 +2809,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499369</v>
+        <v>499319</v>
       </c>
       <c r="R17" t="n">
-        <v>7016923</v>
+        <v>7016956</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2855,7 +2849,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2890,12 +2884,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2913,10 +2907,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120276443</v>
+        <v>120274378</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2925,58 +2919,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499460</v>
+        <v>499337</v>
       </c>
       <c r="R18" t="n">
-        <v>7016990</v>
+        <v>7017015</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3013,7 +2998,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3033,7 +3018,27 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3051,10 +3056,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120276314</v>
+        <v>120275293</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3063,52 +3068,61 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499419</v>
+        <v>499319</v>
       </c>
       <c r="R19" t="n">
-        <v>7016971</v>
+        <v>7016956</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3142,7 +3156,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3163,26 +3177,6 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3200,10 +3194,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273132</v>
+        <v>120275534</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3212,58 +3206,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499362</v>
+        <v>499369</v>
       </c>
       <c r="R20" t="n">
-        <v>7017047</v>
+        <v>7016923</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3300,7 +3281,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3321,6 +3302,26 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3338,10 +3339,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120277714</v>
+        <v>120277899</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3350,41 +3351,58 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499640</v>
+        <v>499598</v>
       </c>
       <c r="R21" t="n">
-        <v>7016917</v>
+        <v>7016864</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3421,7 +3439,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3442,26 +3460,6 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3479,10 +3477,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120272977</v>
+        <v>120278324</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3495,53 +3493,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499347</v>
+        <v>499536</v>
       </c>
       <c r="R22" t="n">
-        <v>7017018</v>
+        <v>7016886</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3575,7 +3568,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3584,6 +3577,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3594,7 +3588,22 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3612,10 +3621,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120274378</v>
+        <v>120275779</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3628,33 +3637,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3663,13 +3664,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499337</v>
+        <v>499408</v>
       </c>
       <c r="R23" t="n">
-        <v>7017015</v>
+        <v>7016909</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3703,7 +3704,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3723,7 +3724,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3736,14 +3737,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3761,10 +3767,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275167</v>
+        <v>120272547</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3796,7 +3802,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3806,7 +3812,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3821,10 +3827,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499357</v>
+        <v>499399</v>
       </c>
       <c r="R24" t="n">
-        <v>7016976</v>
+        <v>7017051</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3861,7 +3867,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3881,7 +3887,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3899,10 +3905,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120275293</v>
+        <v>120278443</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3911,43 +3917,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3955,17 +3957,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499319</v>
+        <v>499314</v>
       </c>
       <c r="R25" t="n">
-        <v>7016956</v>
+        <v>7016944</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3999,7 +4001,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4008,7 +4010,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -4019,7 +4020,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4037,10 +4038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120276615</v>
+        <v>120277809</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4049,61 +4050,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499484</v>
+        <v>499618</v>
       </c>
       <c r="R26" t="n">
-        <v>7016963</v>
+        <v>7016885</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4137,7 +4121,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4157,7 +4141,27 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4175,10 +4179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120277525</v>
+        <v>120272665</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4210,7 +4214,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4220,7 +4224,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -4235,10 +4239,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499634</v>
+        <v>499381</v>
       </c>
       <c r="R27" t="n">
-        <v>7016955</v>
+        <v>7017041</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4275,7 +4279,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4295,7 +4299,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4313,10 +4317,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120272547</v>
+        <v>120275167</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4348,7 +4352,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4358,7 +4362,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -4373,10 +4377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499399</v>
+        <v>499357</v>
       </c>
       <c r="R28" t="n">
-        <v>7017051</v>
+        <v>7016976</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4413,7 +4417,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4433,7 +4437,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4451,10 +4455,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120273861</v>
+        <v>120276314</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4463,58 +4467,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499335</v>
+        <v>499419</v>
       </c>
       <c r="R29" t="n">
-        <v>7017016</v>
+        <v>7016971</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4551,7 +4546,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4571,7 +4566,27 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4589,10 +4604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120275779</v>
+        <v>120273132</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4601,41 +4616,58 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499408</v>
+        <v>499362</v>
       </c>
       <c r="R30" t="n">
-        <v>7016909</v>
+        <v>7017047</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4672,7 +4704,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4692,32 +4724,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4735,10 +4742,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120277809</v>
+        <v>120272977</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>57473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4751,40 +4758,53 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499618</v>
+        <v>499347</v>
       </c>
       <c r="R31" t="n">
-        <v>7016885</v>
+        <v>7017018</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4818,7 +4838,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4827,7 +4847,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4838,27 +4857,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4876,10 +4875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120278049</v>
+        <v>120276443</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4911,7 +4910,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4921,7 +4920,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -4936,10 +4935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499546</v>
+        <v>499460</v>
       </c>
       <c r="R32" t="n">
-        <v>7016839</v>
+        <v>7016990</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4976,7 +4975,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4996,7 +4995,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5014,10 +5013,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120275394</v>
+        <v>120278049</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5026,41 +5025,58 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499319</v>
+        <v>499546</v>
       </c>
       <c r="R33" t="n">
-        <v>7016956</v>
+        <v>7016839</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5097,7 +5113,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5117,27 +5133,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5158,7 +5154,7 @@
         <v>120273613</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5293,10 +5289,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120277582</v>
+        <v>120276956</v>
       </c>
       <c r="B35" t="n">
-        <v>96862</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5305,38 +5301,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499634</v>
+        <v>499543</v>
       </c>
       <c r="R35" t="n">
-        <v>7016955</v>
+        <v>7016946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120272665</v>
+        <v>120273384</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499381</v>
+        <v>499362</v>
       </c>
       <c r="R36" t="n">
-        <v>7017041</v>
+        <v>7017033</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5565,10 +5565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120273384</v>
+        <v>120276615</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5625,13 +5625,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499362</v>
+        <v>499484</v>
       </c>
       <c r="R37" t="n">
-        <v>7017033</v>
+        <v>7016963</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120276956</v>
+        <v>120277525</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499543</v>
+        <v>499634</v>
       </c>
       <c r="R38" t="n">
-        <v>7016946</v>
+        <v>7016955</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120279007</v>
+        <v>120278994</v>
       </c>
       <c r="B39" t="n">
-        <v>90558</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5853,52 +5853,61 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499409</v>
+        <v>499337</v>
       </c>
       <c r="R39" t="n">
-        <v>7017042</v>
+        <v>7017015</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5932,7 +5941,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5953,26 +5962,6 @@
       <c r="AI39" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5990,10 +5979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120278994</v>
+        <v>120279007</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>90576</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6002,61 +5991,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499337</v>
+        <v>499409</v>
       </c>
       <c r="R40" t="n">
-        <v>7017015</v>
+        <v>7017042</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6090,7 +6070,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6111,6 +6091,26 @@
       <c r="AI40" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120277582</v>
+        <v>120277714</v>
       </c>
       <c r="B13" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,57 +2216,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499634</v>
+        <v>499640</v>
       </c>
       <c r="R13" t="n">
-        <v>7016955</v>
+        <v>7016917</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2300,7 +2287,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2320,7 +2307,27 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2487,10 +2494,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120277714</v>
+        <v>120277582</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2499,44 +2506,57 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499640</v>
+        <v>499634</v>
       </c>
       <c r="R15" t="n">
-        <v>7016917</v>
+        <v>7016955</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2570,7 +2590,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2590,27 +2610,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120274378</v>
+        <v>120275293</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2919,49 +2919,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499337</v>
+        <v>499319</v>
       </c>
       <c r="R18" t="n">
-        <v>7017015</v>
+        <v>7016956</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2998,7 +3007,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3018,27 +3027,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3056,10 +3045,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120275293</v>
+        <v>120274378</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3068,58 +3057,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499319</v>
+        <v>499337</v>
       </c>
       <c r="R19" t="n">
-        <v>7016956</v>
+        <v>7017015</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3156,7 +3136,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3176,7 +3156,27 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120275534</v>
+        <v>120277899</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3206,48 +3206,61 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499369</v>
+        <v>499598</v>
       </c>
       <c r="R20" t="n">
-        <v>7016923</v>
+        <v>7016864</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3281,7 +3294,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3301,27 +3314,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3339,10 +3332,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120277899</v>
+        <v>120275534</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3351,61 +3344,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499598</v>
+        <v>499369</v>
       </c>
       <c r="R21" t="n">
-        <v>7016864</v>
+        <v>7016923</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3439,7 +3419,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3459,7 +3439,27 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275167</v>
+        <v>120276314</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4329,61 +4329,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499357</v>
+        <v>499419</v>
       </c>
       <c r="R28" t="n">
-        <v>7016976</v>
+        <v>7016971</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4417,7 +4408,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4437,7 +4428,27 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4455,10 +4466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120276314</v>
+        <v>120275167</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4467,52 +4478,61 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499419</v>
+        <v>499357</v>
       </c>
       <c r="R29" t="n">
-        <v>7016971</v>
+        <v>7016976</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4546,7 +4566,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4566,27 +4586,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120277714</v>
+        <v>120277525</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,44 +2216,61 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499640</v>
+        <v>499634</v>
       </c>
       <c r="R13" t="n">
-        <v>7016917</v>
+        <v>7016955</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2287,7 +2304,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2307,27 +2324,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2345,10 +2342,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120277408</v>
+        <v>120272547</v>
       </c>
       <c r="B14" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2357,49 +2354,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499566</v>
+        <v>499399</v>
       </c>
       <c r="R14" t="n">
-        <v>7016949</v>
+        <v>7017051</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2436,7 +2442,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2456,27 +2462,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2494,10 +2480,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120277582</v>
+        <v>120275779</v>
       </c>
       <c r="B15" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2506,54 +2492,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499634</v>
+        <v>499408</v>
       </c>
       <c r="R15" t="n">
-        <v>7016955</v>
+        <v>7016909</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2590,7 +2563,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2610,7 +2583,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2628,10 +2626,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120273861</v>
+        <v>120277809</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2640,58 +2638,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499335</v>
+        <v>499618</v>
       </c>
       <c r="R16" t="n">
-        <v>7017016</v>
+        <v>7016885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2728,7 +2709,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2748,7 +2729,27 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2766,10 +2767,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120275394</v>
+        <v>120275293</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2778,31 +2779,48 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
@@ -2849,7 +2867,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2869,27 +2887,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2907,10 +2905,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120275293</v>
+        <v>120277408</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2919,58 +2917,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499319</v>
+        <v>499566</v>
       </c>
       <c r="R18" t="n">
-        <v>7016956</v>
+        <v>7016949</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3007,7 +2996,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3027,7 +3016,27 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3045,10 +3054,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120274378</v>
+        <v>120272977</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3061,48 +3070,53 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499337</v>
+        <v>499347</v>
       </c>
       <c r="R19" t="n">
-        <v>7017015</v>
+        <v>7017018</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3136,7 +3150,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3145,7 +3159,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3157,26 +3170,6 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3194,7 +3187,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120277899</v>
+        <v>120276615</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -3229,7 +3222,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3239,7 +3232,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3254,10 +3247,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499598</v>
+        <v>499484</v>
       </c>
       <c r="R20" t="n">
-        <v>7016864</v>
+        <v>7016963</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3294,7 +3287,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3314,7 +3307,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3332,10 +3325,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120275534</v>
+        <v>120273384</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3344,45 +3337,58 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499369</v>
+        <v>499362</v>
       </c>
       <c r="R21" t="n">
-        <v>7016923</v>
+        <v>7017033</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3419,7 +3425,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3440,26 +3446,6 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3477,10 +3463,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120278324</v>
+        <v>120276443</v>
       </c>
       <c r="B22" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3489,52 +3475,61 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499536</v>
+        <v>499460</v>
       </c>
       <c r="R22" t="n">
-        <v>7016886</v>
+        <v>7016990</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3568,7 +3563,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3588,22 +3583,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3621,10 +3601,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275779</v>
+        <v>120278049</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3633,44 +3613,61 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499408</v>
+        <v>499546</v>
       </c>
       <c r="R23" t="n">
-        <v>7016909</v>
+        <v>7016839</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3704,7 +3701,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3724,32 +3721,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3767,10 +3739,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120272547</v>
+        <v>120277714</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3779,58 +3751,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499399</v>
+        <v>499640</v>
       </c>
       <c r="R24" t="n">
-        <v>7017051</v>
+        <v>7016917</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3867,7 +3822,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3887,7 +3842,27 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3905,10 +3880,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120278443</v>
+        <v>120274378</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3921,53 +3896,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499314</v>
+        <v>499337</v>
       </c>
       <c r="R25" t="n">
-        <v>7016944</v>
+        <v>7017015</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -4001,7 +3971,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4010,6 +3980,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -4020,7 +3991,27 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4038,10 +4029,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120277809</v>
+        <v>120276314</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4054,25 +4045,33 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -4081,10 +4080,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499618</v>
+        <v>499419</v>
       </c>
       <c r="R26" t="n">
-        <v>7016885</v>
+        <v>7016971</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4121,7 +4120,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4141,7 +4140,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4156,12 +4155,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4179,7 +4178,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120272665</v>
+        <v>120277899</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -4214,7 +4213,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4224,7 +4223,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -4239,13 +4238,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499381</v>
+        <v>499598</v>
       </c>
       <c r="R27" t="n">
-        <v>7017041</v>
+        <v>7016864</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4279,7 +4278,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4299,7 +4298,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4317,10 +4316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120276314</v>
+        <v>120276956</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4329,49 +4328,58 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499419</v>
+        <v>499543</v>
       </c>
       <c r="R28" t="n">
-        <v>7016971</v>
+        <v>7016946</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4408,7 +4416,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4428,27 +4436,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4466,7 +4454,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120275167</v>
+        <v>120273861</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -4501,7 +4489,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4511,7 +4499,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4526,13 +4514,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499357</v>
+        <v>499335</v>
       </c>
       <c r="R29" t="n">
-        <v>7016976</v>
+        <v>7017016</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4566,7 +4554,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4586,7 +4574,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4742,10 +4730,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120272977</v>
+        <v>120275534</v>
       </c>
       <c r="B31" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4758,53 +4746,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499347</v>
+        <v>499369</v>
       </c>
       <c r="R31" t="n">
-        <v>7017018</v>
+        <v>7016923</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4838,7 +4817,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4847,6 +4826,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4858,6 +4838,26 @@
       <c r="AI31" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120276443</v>
+        <v>120275394</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4887,58 +4887,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499460</v>
+        <v>499319</v>
       </c>
       <c r="R32" t="n">
-        <v>7016990</v>
+        <v>7016956</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4975,7 +4958,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4995,7 +4978,27 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5013,7 +5016,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120278049</v>
+        <v>120272665</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -5048,7 +5051,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5058,7 +5061,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -5073,13 +5076,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499546</v>
+        <v>499381</v>
       </c>
       <c r="R33" t="n">
-        <v>7016839</v>
+        <v>7017041</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5113,7 +5116,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5133,7 +5136,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5151,7 +5154,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120273613</v>
+        <v>120275167</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -5186,7 +5189,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5196,7 +5199,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -5211,13 +5214,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499334</v>
+        <v>499357</v>
       </c>
       <c r="R34" t="n">
-        <v>7017033</v>
+        <v>7016976</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5251,7 +5254,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5271,7 +5274,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5289,10 +5292,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120276956</v>
+        <v>120278443</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5301,43 +5304,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5345,14 +5344,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499543</v>
+        <v>499314</v>
       </c>
       <c r="R35" t="n">
-        <v>7016946</v>
+        <v>7016944</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5389,7 +5388,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5398,7 +5397,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5409,7 +5407,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5427,7 +5425,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120273384</v>
+        <v>120273613</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -5462,7 +5460,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5487,7 +5485,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499362</v>
+        <v>499334</v>
       </c>
       <c r="R36" t="n">
         <v>7017033</v>
@@ -5527,7 +5525,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5565,10 +5563,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120276615</v>
+        <v>120277582</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5577,42 +5575,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
@@ -5625,13 +5619,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499484</v>
+        <v>499634</v>
       </c>
       <c r="R37" t="n">
-        <v>7016963</v>
+        <v>7016955</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5665,7 +5659,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5685,7 +5679,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5703,10 +5697,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120277525</v>
+        <v>120278324</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5715,58 +5709,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499634</v>
+        <v>499536</v>
       </c>
       <c r="R38" t="n">
-        <v>7016955</v>
+        <v>7016886</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5803,7 +5788,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5823,7 +5808,22 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120277525</v>
+        <v>120272977</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,43 +2216,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2260,17 +2256,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499634</v>
+        <v>499347</v>
       </c>
       <c r="R13" t="n">
-        <v>7016955</v>
+        <v>7017018</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2304,7 +2300,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2313,7 +2309,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2324,7 +2319,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2342,10 +2337,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120272547</v>
+        <v>120275779</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2354,61 +2349,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499399</v>
+        <v>499408</v>
       </c>
       <c r="R14" t="n">
-        <v>7017051</v>
+        <v>7016909</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2442,7 +2420,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2462,7 +2440,32 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2480,10 +2483,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120275779</v>
+        <v>120273132</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2492,41 +2495,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499408</v>
+        <v>499362</v>
       </c>
       <c r="R15" t="n">
-        <v>7016909</v>
+        <v>7017047</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2563,7 +2583,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2583,32 +2603,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2767,10 +2762,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120275293</v>
+        <v>120277582</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2779,25 +2774,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2807,14 +2802,10 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -2827,13 +2818,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499319</v>
+        <v>499634</v>
       </c>
       <c r="R17" t="n">
-        <v>7016956</v>
+        <v>7016955</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2867,7 +2858,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2887,7 +2878,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2905,10 +2896,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120277408</v>
+        <v>120272547</v>
       </c>
       <c r="B18" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2917,49 +2908,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499566</v>
+        <v>499399</v>
       </c>
       <c r="R18" t="n">
-        <v>7016949</v>
+        <v>7017051</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3016,27 +3016,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3054,10 +3034,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120272977</v>
+        <v>120278049</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3066,39 +3046,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3106,17 +3090,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499347</v>
+        <v>499546</v>
       </c>
       <c r="R19" t="n">
-        <v>7017018</v>
+        <v>7016839</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3150,7 +3134,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3159,6 +3143,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3169,7 +3154,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3187,7 +3172,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120276615</v>
+        <v>120273861</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -3222,7 +3207,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3232,7 +3217,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3247,13 +3232,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499484</v>
+        <v>499335</v>
       </c>
       <c r="R20" t="n">
-        <v>7016963</v>
+        <v>7017016</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3287,7 +3272,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3307,7 +3292,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3325,7 +3310,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120273384</v>
+        <v>120276615</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3360,7 +3345,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3370,7 +3355,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3385,13 +3370,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499362</v>
+        <v>499484</v>
       </c>
       <c r="R21" t="n">
-        <v>7017033</v>
+        <v>7016963</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3425,7 +3410,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3445,7 +3430,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3463,7 +3448,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120276443</v>
+        <v>120273613</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3498,7 +3483,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3508,7 +3493,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3523,13 +3508,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499460</v>
+        <v>499334</v>
       </c>
       <c r="R22" t="n">
-        <v>7016990</v>
+        <v>7017033</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3563,7 +3548,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3583,7 +3568,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3601,7 +3586,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120278049</v>
+        <v>120275293</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3636,7 +3621,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3646,7 +3631,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3661,10 +3646,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499546</v>
+        <v>499319</v>
       </c>
       <c r="R23" t="n">
-        <v>7016839</v>
+        <v>7016956</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3701,7 +3686,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3721,7 +3706,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3739,10 +3724,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120277714</v>
+        <v>120277899</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3751,41 +3736,58 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499640</v>
+        <v>499598</v>
       </c>
       <c r="R24" t="n">
-        <v>7016917</v>
+        <v>7016864</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3822,7 +3824,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3843,26 +3845,6 @@
       <c r="AI24" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3880,10 +3862,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120274378</v>
+        <v>120277525</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3892,52 +3874,61 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499337</v>
+        <v>499634</v>
       </c>
       <c r="R25" t="n">
-        <v>7017015</v>
+        <v>7016955</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3971,7 +3962,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3991,27 +3982,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4029,10 +4000,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120276314</v>
+        <v>120278324</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4045,26 +4016,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4080,10 +4051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499419</v>
+        <v>499536</v>
       </c>
       <c r="R26" t="n">
-        <v>7016971</v>
+        <v>7016886</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4120,7 +4091,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4140,7 +4111,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4153,14 +4124,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4178,10 +4144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120277899</v>
+        <v>120275534</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4190,61 +4156,48 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499598</v>
+        <v>499369</v>
       </c>
       <c r="R27" t="n">
-        <v>7016864</v>
+        <v>7016923</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4278,7 +4231,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4298,7 +4251,27 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4454,7 +4427,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120273861</v>
+        <v>120272665</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -4489,7 +4462,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4499,7 +4472,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4514,10 +4487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499335</v>
+        <v>499381</v>
       </c>
       <c r="R29" t="n">
-        <v>7017016</v>
+        <v>7017041</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4554,7 +4527,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4592,10 +4565,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120273132</v>
+        <v>120275394</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4604,61 +4577,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499362</v>
+        <v>499319</v>
       </c>
       <c r="R30" t="n">
-        <v>7017047</v>
+        <v>7016956</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4692,7 +4648,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4713,6 +4669,26 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4730,10 +4706,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120275534</v>
+        <v>120278443</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4746,41 +4722,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499369</v>
+        <v>499314</v>
       </c>
       <c r="R31" t="n">
-        <v>7016923</v>
+        <v>7016944</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4817,7 +4802,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4826,7 +4811,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4837,27 +4821,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4875,10 +4839,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120275394</v>
+        <v>120277408</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4891,25 +4855,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4918,10 +4890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499319</v>
+        <v>499566</v>
       </c>
       <c r="R32" t="n">
-        <v>7016956</v>
+        <v>7016949</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4958,7 +4930,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4978,7 +4950,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4998,7 +4970,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5016,10 +4988,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120272665</v>
+        <v>120274378</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5028,61 +5000,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499381</v>
+        <v>499337</v>
       </c>
       <c r="R33" t="n">
-        <v>7017041</v>
+        <v>7017015</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5116,7 +5079,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5137,6 +5100,26 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5292,10 +5275,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120278443</v>
+        <v>120273384</v>
       </c>
       <c r="B35" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5304,39 +5287,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5344,14 +5331,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499314</v>
+        <v>499362</v>
       </c>
       <c r="R35" t="n">
-        <v>7016944</v>
+        <v>7017033</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5388,7 +5375,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5397,6 +5384,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5407,7 +5395,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5425,10 +5413,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120273613</v>
+        <v>120277714</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5437,61 +5425,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499334</v>
+        <v>499640</v>
       </c>
       <c r="R36" t="n">
-        <v>7017033</v>
+        <v>7016917</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5525,7 +5496,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5545,7 +5516,27 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5563,10 +5554,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120277582</v>
+        <v>120276314</v>
       </c>
       <c r="B37" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5575,54 +5566,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499634</v>
+        <v>499419</v>
       </c>
       <c r="R37" t="n">
-        <v>7016955</v>
+        <v>7016971</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5659,7 +5645,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5679,7 +5665,27 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5697,10 +5703,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120278324</v>
+        <v>120276443</v>
       </c>
       <c r="B38" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5709,52 +5715,61 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499536</v>
+        <v>499460</v>
       </c>
       <c r="R38" t="n">
-        <v>7016886</v>
+        <v>7016990</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5788,7 +5803,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5808,22 +5823,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -4839,10 +4839,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120277408</v>
+        <v>120274378</v>
       </c>
       <c r="B32" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4855,26 +4855,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499566</v>
+        <v>499337</v>
       </c>
       <c r="R32" t="n">
-        <v>7016949</v>
+        <v>7017015</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120274378</v>
+        <v>120277408</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5004,26 +5004,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499337</v>
+        <v>499566</v>
       </c>
       <c r="R33" t="n">
-        <v>7017015</v>
+        <v>7016949</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120272977</v>
+        <v>120277899</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,39 +2216,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2256,17 +2260,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499347</v>
+        <v>499598</v>
       </c>
       <c r="R13" t="n">
-        <v>7017018</v>
+        <v>7016864</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2300,7 +2304,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2309,6 +2313,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2319,7 +2324,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2337,7 +2342,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120275779</v>
+        <v>120275534</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2370,7 +2375,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2380,10 +2389,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499408</v>
+        <v>499369</v>
       </c>
       <c r="R14" t="n">
-        <v>7016909</v>
+        <v>7016923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2420,7 +2429,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2440,7 +2449,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2453,11 +2462,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM14" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2465,7 +2469,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2483,7 +2487,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120273132</v>
+        <v>120272665</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2518,7 +2522,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2528,7 +2532,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2543,10 +2547,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499362</v>
+        <v>499381</v>
       </c>
       <c r="R15" t="n">
-        <v>7017047</v>
+        <v>7017041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2583,7 +2587,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2621,10 +2625,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120277809</v>
+        <v>120273384</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2633,41 +2637,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499618</v>
+        <v>499362</v>
       </c>
       <c r="R16" t="n">
-        <v>7016885</v>
+        <v>7017033</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2704,7 +2725,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2724,27 +2745,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2762,10 +2763,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120277582</v>
+        <v>120273613</v>
       </c>
       <c r="B17" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2774,38 +2775,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -2818,10 +2823,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499634</v>
+        <v>499334</v>
       </c>
       <c r="R17" t="n">
-        <v>7016955</v>
+        <v>7017033</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2858,7 +2863,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2878,7 +2883,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2896,10 +2901,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120272547</v>
+        <v>120277408</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2908,58 +2913,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499399</v>
+        <v>499566</v>
       </c>
       <c r="R18" t="n">
-        <v>7017051</v>
+        <v>7016949</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2996,7 +2992,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3016,7 +3012,27 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3034,10 +3050,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120278049</v>
+        <v>120277809</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3046,61 +3062,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499546</v>
+        <v>499618</v>
       </c>
       <c r="R19" t="n">
-        <v>7016839</v>
+        <v>7016885</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3134,7 +3133,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3155,6 +3154,26 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3172,10 +3191,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273861</v>
+        <v>120275394</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3184,61 +3203,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499335</v>
+        <v>499319</v>
       </c>
       <c r="R20" t="n">
-        <v>7017016</v>
+        <v>7016956</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3272,7 +3274,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,6 +3295,26 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3310,7 +3332,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120276615</v>
+        <v>120273132</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3345,7 +3367,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3355,7 +3377,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3370,13 +3392,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499484</v>
+        <v>499362</v>
       </c>
       <c r="R21" t="n">
-        <v>7016963</v>
+        <v>7017047</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3410,7 +3432,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3430,7 +3452,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3448,10 +3470,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120273613</v>
+        <v>120272977</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3460,43 +3482,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3504,17 +3522,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499334</v>
+        <v>499347</v>
       </c>
       <c r="R22" t="n">
-        <v>7017033</v>
+        <v>7017018</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3548,7 +3566,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3557,7 +3575,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3586,10 +3603,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275293</v>
+        <v>120275779</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3598,61 +3615,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499319</v>
+        <v>499408</v>
       </c>
       <c r="R23" t="n">
-        <v>7016956</v>
+        <v>7016909</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3707,6 +3707,31 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3724,7 +3749,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120277899</v>
+        <v>120276443</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3759,7 +3784,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3769,7 +3794,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3784,10 +3809,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499598</v>
+        <v>499460</v>
       </c>
       <c r="R24" t="n">
-        <v>7016864</v>
+        <v>7016990</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3824,7 +3849,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3844,7 +3869,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3862,7 +3887,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120277525</v>
+        <v>120278049</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3897,7 +3922,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3922,13 +3947,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499634</v>
+        <v>499546</v>
       </c>
       <c r="R25" t="n">
-        <v>7016955</v>
+        <v>7016839</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3962,7 +3987,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3982,7 +4007,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4000,10 +4025,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120278324</v>
+        <v>120278443</v>
       </c>
       <c r="B26" t="n">
-        <v>90576</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4016,45 +4041,50 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499536</v>
+        <v>499314</v>
       </c>
       <c r="R26" t="n">
-        <v>7016886</v>
+        <v>7016944</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4091,7 +4121,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4100,7 +4130,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4111,22 +4140,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4144,10 +4158,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275534</v>
+        <v>120275167</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4156,48 +4170,61 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499369</v>
+        <v>499357</v>
       </c>
       <c r="R27" t="n">
-        <v>7016923</v>
+        <v>7016976</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4231,7 +4258,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4251,27 +4278,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4289,10 +4296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120276956</v>
+        <v>120277582</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4301,42 +4308,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
@@ -4349,10 +4352,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499543</v>
+        <v>499634</v>
       </c>
       <c r="R28" t="n">
-        <v>7016946</v>
+        <v>7016955</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4389,7 +4392,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4427,10 +4430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120272665</v>
+        <v>120274378</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4439,61 +4442,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499381</v>
+        <v>499337</v>
       </c>
       <c r="R29" t="n">
-        <v>7017041</v>
+        <v>7017015</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4527,7 +4521,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4548,6 +4542,26 @@
       <c r="AI29" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4565,10 +4579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120275394</v>
+        <v>120278324</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4581,25 +4595,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -4608,13 +4630,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499319</v>
+        <v>499536</v>
       </c>
       <c r="R30" t="n">
-        <v>7016956</v>
+        <v>7016886</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4648,7 +4670,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4668,7 +4690,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4681,14 +4703,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4706,10 +4723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120278443</v>
+        <v>120276615</v>
       </c>
       <c r="B31" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4718,39 +4735,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4758,17 +4779,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499314</v>
+        <v>499484</v>
       </c>
       <c r="R31" t="n">
-        <v>7016944</v>
+        <v>7016963</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4802,7 +4823,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4811,6 +4832,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4821,7 +4843,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4839,10 +4861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120274378</v>
+        <v>120272547</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4851,49 +4873,58 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499337</v>
+        <v>499399</v>
       </c>
       <c r="R32" t="n">
-        <v>7017015</v>
+        <v>7017051</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4930,7 +4961,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4951,26 +4982,6 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4988,10 +4999,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120277408</v>
+        <v>120277525</v>
       </c>
       <c r="B33" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5000,52 +5011,61 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499566</v>
+        <v>499634</v>
       </c>
       <c r="R33" t="n">
-        <v>7016949</v>
+        <v>7016955</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5079,7 +5099,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5100,26 +5120,6 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5137,7 +5137,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120275167</v>
+        <v>120275293</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499357</v>
+        <v>499319</v>
       </c>
       <c r="R34" t="n">
-        <v>7016976</v>
+        <v>7016956</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120273384</v>
+        <v>120276314</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5287,58 +5287,49 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499362</v>
+        <v>499419</v>
       </c>
       <c r="R35" t="n">
-        <v>7017033</v>
+        <v>7016971</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5375,7 +5366,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5395,7 +5386,27 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5554,10 +5565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120276314</v>
+        <v>120276956</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5566,49 +5577,58 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499419</v>
+        <v>499543</v>
       </c>
       <c r="R37" t="n">
-        <v>7016971</v>
+        <v>7016946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5645,7 +5665,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5665,27 +5685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5703,7 +5703,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120276443</v>
+        <v>120273861</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499460</v>
+        <v>499335</v>
       </c>
       <c r="R38" t="n">
-        <v>7016990</v>
+        <v>7017016</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120277899</v>
+        <v>120275534</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,61 +2216,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499598</v>
+        <v>499369</v>
       </c>
       <c r="R13" t="n">
-        <v>7016864</v>
+        <v>7016923</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2304,7 +2291,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2324,7 +2311,27 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2342,10 +2349,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120275534</v>
+        <v>120273384</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2354,45 +2361,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499369</v>
+        <v>499362</v>
       </c>
       <c r="R14" t="n">
-        <v>7016923</v>
+        <v>7017033</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2429,7 +2449,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2450,26 +2470,6 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120273384</v>
+        <v>120278324</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2637,58 +2637,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499362</v>
+        <v>499536</v>
       </c>
       <c r="R16" t="n">
-        <v>7017033</v>
+        <v>7016886</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2725,7 +2716,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2745,7 +2736,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2763,10 +2769,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120273613</v>
+        <v>120275394</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2775,61 +2781,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499334</v>
+        <v>499319</v>
       </c>
       <c r="R17" t="n">
-        <v>7017033</v>
+        <v>7016956</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2863,7 +2852,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2884,6 +2873,26 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120277408</v>
+        <v>120276314</v>
       </c>
       <c r="B18" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2917,26 +2926,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2952,13 +2961,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499566</v>
+        <v>499419</v>
       </c>
       <c r="R18" t="n">
-        <v>7016949</v>
+        <v>7016971</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2992,7 +3001,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3012,7 +3021,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3027,12 +3036,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3050,10 +3059,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120277809</v>
+        <v>120272547</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3062,44 +3071,61 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499618</v>
+        <v>499399</v>
       </c>
       <c r="R19" t="n">
-        <v>7016885</v>
+        <v>7017051</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3133,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3153,27 +3179,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3191,10 +3197,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120275394</v>
+        <v>120273861</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3203,44 +3209,61 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499319</v>
+        <v>499335</v>
       </c>
       <c r="R20" t="n">
-        <v>7016956</v>
+        <v>7017016</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3274,7 +3297,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3295,26 +3318,6 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3332,7 +3335,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120273132</v>
+        <v>120273613</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3367,7 +3370,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3392,10 +3395,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499362</v>
+        <v>499334</v>
       </c>
       <c r="R21" t="n">
-        <v>7017047</v>
+        <v>7017033</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3432,7 +3435,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3470,10 +3473,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120272977</v>
+        <v>120276443</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3482,39 +3485,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3522,17 +3529,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499347</v>
+        <v>499460</v>
       </c>
       <c r="R22" t="n">
-        <v>7017018</v>
+        <v>7016990</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3566,7 +3573,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3575,6 +3582,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3585,7 +3593,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3603,10 +3611,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275779</v>
+        <v>120277899</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3615,44 +3623,61 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499408</v>
+        <v>499598</v>
       </c>
       <c r="R23" t="n">
-        <v>7016909</v>
+        <v>7016864</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3686,7 +3711,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3706,32 +3731,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120276443</v>
+        <v>120273132</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3809,13 +3809,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499460</v>
+        <v>499362</v>
       </c>
       <c r="R24" t="n">
-        <v>7016990</v>
+        <v>7017047</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120278049</v>
+        <v>120277809</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3899,61 +3899,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499546</v>
+        <v>499618</v>
       </c>
       <c r="R25" t="n">
-        <v>7016839</v>
+        <v>7016885</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3987,7 +3970,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4008,6 +3991,26 @@
       <c r="AI25" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4025,10 +4028,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120278443</v>
+        <v>120277582</v>
       </c>
       <c r="B26" t="n">
-        <v>57473</v>
+        <v>96885</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4037,39 +4040,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4077,14 +4080,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499314</v>
+        <v>499634</v>
       </c>
       <c r="R26" t="n">
-        <v>7016944</v>
+        <v>7016955</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4121,7 +4124,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4130,6 +4133,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4140,7 +4144,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4158,7 +4162,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275167</v>
+        <v>120277525</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -4193,7 +4197,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4203,7 +4207,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -4218,13 +4222,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499357</v>
+        <v>499634</v>
       </c>
       <c r="R27" t="n">
-        <v>7016976</v>
+        <v>7016955</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4258,7 +4262,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4278,7 +4282,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4296,10 +4300,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120277582</v>
+        <v>120277714</v>
       </c>
       <c r="B28" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4308,57 +4312,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499634</v>
+        <v>499640</v>
       </c>
       <c r="R28" t="n">
-        <v>7016955</v>
+        <v>7016917</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4392,7 +4383,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4412,7 +4403,27 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4430,10 +4441,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120274378</v>
+        <v>120277408</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4446,26 +4457,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4481,10 +4492,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499337</v>
+        <v>499566</v>
       </c>
       <c r="R29" t="n">
-        <v>7017015</v>
+        <v>7016949</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4521,7 +4532,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4541,7 +4552,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4561,7 +4572,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4579,10 +4590,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120278324</v>
+        <v>120276615</v>
       </c>
       <c r="B30" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4591,52 +4602,61 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499536</v>
+        <v>499484</v>
       </c>
       <c r="R30" t="n">
-        <v>7016886</v>
+        <v>7016963</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4670,7 +4690,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4690,22 +4710,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4723,7 +4728,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120276615</v>
+        <v>120278049</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -4758,7 +4763,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4768,7 +4773,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4783,10 +4788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499484</v>
+        <v>499546</v>
       </c>
       <c r="R31" t="n">
-        <v>7016963</v>
+        <v>7016839</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4823,7 +4828,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4843,7 +4848,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4861,10 +4866,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120272547</v>
+        <v>120278443</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4873,43 +4878,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4917,17 +4918,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499399</v>
+        <v>499314</v>
       </c>
       <c r="R32" t="n">
-        <v>7017051</v>
+        <v>7016944</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4961,7 +4962,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4970,7 +4971,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120277525</v>
+        <v>120274378</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5011,61 +5011,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499634</v>
+        <v>499337</v>
       </c>
       <c r="R33" t="n">
-        <v>7016955</v>
+        <v>7017015</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5099,7 +5090,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5119,7 +5110,27 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5137,7 +5148,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120275293</v>
+        <v>120276956</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -5172,7 +5183,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5197,13 +5208,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499319</v>
+        <v>499543</v>
       </c>
       <c r="R34" t="n">
-        <v>7016956</v>
+        <v>7016946</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5237,7 +5248,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5257,7 +5268,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5275,10 +5286,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120276314</v>
+        <v>120275293</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5287,52 +5298,61 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499419</v>
+        <v>499319</v>
       </c>
       <c r="R35" t="n">
-        <v>7016971</v>
+        <v>7016956</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5366,7 +5386,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5387,26 +5407,6 @@
       <c r="AI35" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5424,7 +5424,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120277714</v>
+        <v>120275779</v>
       </c>
       <c r="B36" t="n">
         <v>78542</v>
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499640</v>
+        <v>499408</v>
       </c>
       <c r="R36" t="n">
-        <v>7016917</v>
+        <v>7016909</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5540,6 +5540,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM36" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -5547,7 +5552,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5565,10 +5570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120276956</v>
+        <v>120272977</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5577,43 +5582,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5621,17 +5622,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499543</v>
+        <v>499347</v>
       </c>
       <c r="R37" t="n">
-        <v>7016946</v>
+        <v>7017018</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5665,7 +5666,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5674,7 +5675,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5703,7 +5703,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120273861</v>
+        <v>120275167</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499335</v>
+        <v>499357</v>
       </c>
       <c r="R38" t="n">
-        <v>7017016</v>
+        <v>7016976</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -4866,10 +4866,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120278443</v>
+        <v>120274378</v>
       </c>
       <c r="B32" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4882,53 +4882,48 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499314</v>
+        <v>499337</v>
       </c>
       <c r="R32" t="n">
-        <v>7016944</v>
+        <v>7017015</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4962,7 +4957,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4971,6 +4966,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4981,7 +4977,27 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4999,10 +5015,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120274378</v>
+        <v>120278443</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5015,48 +5031,53 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499337</v>
+        <v>499314</v>
       </c>
       <c r="R33" t="n">
-        <v>7017015</v>
+        <v>7016944</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5090,7 +5111,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5099,7 +5120,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5110,27 +5130,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120275534</v>
+        <v>120277582</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,45 +2216,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499369</v>
+        <v>499634</v>
       </c>
       <c r="R13" t="n">
-        <v>7016923</v>
+        <v>7016955</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2291,7 +2300,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2311,27 +2320,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2349,7 +2338,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120273384</v>
+        <v>120272547</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2384,7 +2373,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2409,13 +2398,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499362</v>
+        <v>499399</v>
       </c>
       <c r="R14" t="n">
-        <v>7017033</v>
+        <v>7017051</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2449,7 +2438,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2487,7 +2476,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120272665</v>
+        <v>120273132</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2522,7 +2511,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2532,7 +2521,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2547,10 +2536,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499381</v>
+        <v>499362</v>
       </c>
       <c r="R15" t="n">
-        <v>7017041</v>
+        <v>7017047</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2587,7 +2576,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2625,10 +2614,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120278324</v>
+        <v>120275394</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2641,33 +2630,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2676,13 +2657,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499536</v>
+        <v>499319</v>
       </c>
       <c r="R16" t="n">
-        <v>7016886</v>
+        <v>7016956</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2716,7 +2697,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2736,7 +2717,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2749,9 +2730,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2769,10 +2755,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120275394</v>
+        <v>120272977</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2785,40 +2771,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499319</v>
+        <v>499347</v>
       </c>
       <c r="R17" t="n">
-        <v>7016956</v>
+        <v>7017018</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2852,7 +2851,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2861,7 +2860,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2873,26 +2871,6 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2910,10 +2888,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120276314</v>
+        <v>120277408</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2926,26 +2904,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2961,13 +2939,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499419</v>
+        <v>499566</v>
       </c>
       <c r="R18" t="n">
-        <v>7016971</v>
+        <v>7016949</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3001,7 +2979,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3021,7 +2999,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3036,12 +3014,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3059,7 +3037,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120272547</v>
+        <v>120275293</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -3094,7 +3072,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3104,7 +3082,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -3119,10 +3097,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499399</v>
+        <v>499319</v>
       </c>
       <c r="R19" t="n">
-        <v>7017051</v>
+        <v>7016956</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3159,7 +3137,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3179,7 +3157,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3197,7 +3175,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273861</v>
+        <v>120277899</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -3232,7 +3210,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3257,13 +3235,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499335</v>
+        <v>499598</v>
       </c>
       <c r="R20" t="n">
-        <v>7017016</v>
+        <v>7016864</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3297,7 +3275,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3317,7 +3295,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3335,7 +3313,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120273613</v>
+        <v>120276615</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3370,7 +3348,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3380,7 +3358,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3395,13 +3373,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499334</v>
+        <v>499484</v>
       </c>
       <c r="R21" t="n">
-        <v>7017033</v>
+        <v>7016963</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3435,7 +3413,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3455,7 +3433,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3473,10 +3451,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120276443</v>
+        <v>120276314</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3485,61 +3463,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499460</v>
+        <v>499419</v>
       </c>
       <c r="R22" t="n">
-        <v>7016990</v>
+        <v>7016971</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3573,7 +3542,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3593,7 +3562,27 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3611,10 +3600,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120277899</v>
+        <v>120277809</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3623,61 +3612,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499598</v>
+        <v>499618</v>
       </c>
       <c r="R23" t="n">
-        <v>7016864</v>
+        <v>7016885</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3711,7 +3683,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3732,6 +3704,26 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3749,7 +3741,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120273132</v>
+        <v>120277525</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3784,7 +3776,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3809,10 +3801,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499362</v>
+        <v>499634</v>
       </c>
       <c r="R24" t="n">
-        <v>7017047</v>
+        <v>7016955</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3849,7 +3841,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3869,7 +3861,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3887,7 +3879,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120277809</v>
+        <v>120275534</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3920,7 +3912,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3930,10 +3926,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499618</v>
+        <v>499369</v>
       </c>
       <c r="R25" t="n">
-        <v>7016885</v>
+        <v>7016923</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3970,7 +3966,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3990,7 +3986,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4010,7 +4006,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4028,10 +4024,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120277582</v>
+        <v>120276956</v>
       </c>
       <c r="B26" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4040,38 +4036,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499634</v>
+        <v>499543</v>
       </c>
       <c r="R26" t="n">
-        <v>7016955</v>
+        <v>7016946</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120277525</v>
+        <v>120274378</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4174,61 +4174,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499634</v>
+        <v>499337</v>
       </c>
       <c r="R27" t="n">
-        <v>7016955</v>
+        <v>7017015</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4262,7 +4253,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4282,7 +4273,27 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4441,7 +4452,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120277408</v>
+        <v>120278324</v>
       </c>
       <c r="B29" t="n">
         <v>90576</v>
@@ -4476,7 +4487,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4492,13 +4503,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499566</v>
+        <v>499536</v>
       </c>
       <c r="R29" t="n">
-        <v>7016949</v>
+        <v>7016886</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4532,7 +4543,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4552,7 +4563,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4565,14 +4576,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4590,7 +4596,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120276615</v>
+        <v>120273384</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -4625,7 +4631,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4635,7 +4641,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -4650,13 +4656,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499484</v>
+        <v>499362</v>
       </c>
       <c r="R30" t="n">
-        <v>7016963</v>
+        <v>7017033</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4690,7 +4696,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4710,7 +4716,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4728,10 +4734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120278049</v>
+        <v>120275779</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4740,61 +4746,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499546</v>
+        <v>499408</v>
       </c>
       <c r="R31" t="n">
-        <v>7016839</v>
+        <v>7016909</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4828,7 +4817,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4848,7 +4837,32 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4866,10 +4880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120274378</v>
+        <v>120272665</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4878,52 +4892,61 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499337</v>
+        <v>499381</v>
       </c>
       <c r="R32" t="n">
-        <v>7017015</v>
+        <v>7017041</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4957,7 +4980,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4978,26 +5001,6 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5015,10 +5018,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120278443</v>
+        <v>120275167</v>
       </c>
       <c r="B33" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5027,39 +5030,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5067,17 +5074,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499314</v>
+        <v>499357</v>
       </c>
       <c r="R33" t="n">
-        <v>7016944</v>
+        <v>7016976</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5111,7 +5118,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5120,6 +5127,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5130,7 +5138,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5148,7 +5156,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120276956</v>
+        <v>120273861</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -5183,7 +5191,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5193,7 +5201,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -5208,10 +5216,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499543</v>
+        <v>499335</v>
       </c>
       <c r="R34" t="n">
-        <v>7016946</v>
+        <v>7017016</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5248,7 +5256,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5268,7 +5276,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5286,10 +5294,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120275293</v>
+        <v>120278443</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5298,43 +5306,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5342,17 +5346,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499319</v>
+        <v>499314</v>
       </c>
       <c r="R35" t="n">
-        <v>7016956</v>
+        <v>7016944</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5386,7 +5390,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5395,7 +5399,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5406,7 +5409,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5424,10 +5427,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120275779</v>
+        <v>120276443</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5436,44 +5439,61 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499408</v>
+        <v>499460</v>
       </c>
       <c r="R36" t="n">
-        <v>7016909</v>
+        <v>7016990</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5507,7 +5527,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5527,32 +5547,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5570,10 +5565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120272977</v>
+        <v>120278049</v>
       </c>
       <c r="B37" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5582,39 +5577,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5622,17 +5621,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499347</v>
+        <v>499546</v>
       </c>
       <c r="R37" t="n">
-        <v>7017018</v>
+        <v>7016839</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5666,7 +5665,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5675,6 +5674,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5703,7 +5703,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120275167</v>
+        <v>120273613</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499357</v>
+        <v>499334</v>
       </c>
       <c r="R38" t="n">
-        <v>7016976</v>
+        <v>7017033</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120278994</v>
+        <v>120279007</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5853,61 +5853,52 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499337</v>
+        <v>499409</v>
       </c>
       <c r="R39" t="n">
-        <v>7017015</v>
+        <v>7017042</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5941,7 +5932,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5962,6 +5953,26 @@
       <c r="AI39" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5979,10 +5990,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120279007</v>
+        <v>120278994</v>
       </c>
       <c r="B40" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5991,52 +6002,61 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499409</v>
+        <v>499337</v>
       </c>
       <c r="R40" t="n">
-        <v>7017042</v>
+        <v>7017015</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6070,7 +6090,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6091,26 +6111,6 @@
       <c r="AI40" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120277582</v>
+        <v>120273132</v>
       </c>
       <c r="B13" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2216,38 +2216,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -2260,10 +2264,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499634</v>
+        <v>499362</v>
       </c>
       <c r="R13" t="n">
-        <v>7016955</v>
+        <v>7017047</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2300,7 +2304,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2320,7 +2324,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2338,10 +2342,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120272547</v>
+        <v>120277582</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2350,42 +2354,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499399</v>
+        <v>499634</v>
       </c>
       <c r="R14" t="n">
-        <v>7017051</v>
+        <v>7016955</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120273132</v>
+        <v>120278324</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2488,58 +2488,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499362</v>
+        <v>499536</v>
       </c>
       <c r="R15" t="n">
-        <v>7017047</v>
+        <v>7016886</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2576,7 +2567,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2596,7 +2587,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2614,7 +2620,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120275394</v>
+        <v>120275534</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2647,7 +2653,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2657,13 +2667,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499319</v>
+        <v>499369</v>
       </c>
       <c r="R16" t="n">
-        <v>7016956</v>
+        <v>7016923</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2697,7 +2707,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2732,12 +2742,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2755,7 +2765,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120272977</v>
+        <v>120278443</v>
       </c>
       <c r="B17" t="n">
         <v>57473</v>
@@ -2811,13 +2821,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499347</v>
+        <v>499314</v>
       </c>
       <c r="R17" t="n">
-        <v>7017018</v>
+        <v>7016944</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2870,7 +2880,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2888,10 +2898,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120277408</v>
+        <v>120276956</v>
       </c>
       <c r="B18" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2900,52 +2910,61 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499566</v>
+        <v>499543</v>
       </c>
       <c r="R18" t="n">
-        <v>7016949</v>
+        <v>7016946</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2979,7 +2998,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3000,26 +3019,6 @@
       <c r="AI18" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3037,7 +3036,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120275293</v>
+        <v>120277899</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -3072,7 +3071,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3082,7 +3081,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -3097,10 +3096,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499319</v>
+        <v>499598</v>
       </c>
       <c r="R19" t="n">
-        <v>7016956</v>
+        <v>7016864</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3137,7 +3136,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3157,7 +3156,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3175,7 +3174,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120277899</v>
+        <v>120275167</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -3210,7 +3209,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3220,7 +3219,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3235,10 +3234,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499598</v>
+        <v>499357</v>
       </c>
       <c r="R20" t="n">
-        <v>7016864</v>
+        <v>7016976</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3275,7 +3274,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3295,7 +3294,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3313,7 +3312,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120276615</v>
+        <v>120275293</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3348,7 +3347,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3373,10 +3372,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499484</v>
+        <v>499319</v>
       </c>
       <c r="R21" t="n">
-        <v>7016963</v>
+        <v>7016956</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3413,7 +3412,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3433,7 +3432,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3451,10 +3450,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120276314</v>
+        <v>120277408</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3467,26 +3466,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3502,13 +3501,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499419</v>
+        <v>499566</v>
       </c>
       <c r="R22" t="n">
-        <v>7016971</v>
+        <v>7016949</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3542,7 +3541,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3562,7 +3561,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3577,12 +3576,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3600,10 +3599,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120277809</v>
+        <v>120276314</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3616,25 +3615,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3643,10 +3650,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499618</v>
+        <v>499419</v>
       </c>
       <c r="R23" t="n">
-        <v>7016885</v>
+        <v>7016971</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3683,7 +3690,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3703,7 +3710,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3718,12 +3725,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3741,7 +3748,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120277525</v>
+        <v>120272547</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3776,7 +3783,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3801,13 +3808,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499634</v>
+        <v>499399</v>
       </c>
       <c r="R24" t="n">
-        <v>7016955</v>
+        <v>7017051</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3841,7 +3848,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3861,7 +3868,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3879,10 +3886,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120275534</v>
+        <v>120272665</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3891,45 +3898,58 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499369</v>
+        <v>499381</v>
       </c>
       <c r="R25" t="n">
-        <v>7016923</v>
+        <v>7017041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3966,7 +3986,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3987,26 +4007,6 @@
       <c r="AI25" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120276956</v>
+        <v>120276443</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4084,13 +4084,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499543</v>
+        <v>499460</v>
       </c>
       <c r="R26" t="n">
-        <v>7016946</v>
+        <v>7016990</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120274378</v>
+        <v>120273861</v>
       </c>
       <c r="B27" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4174,52 +4174,61 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499337</v>
+        <v>499335</v>
       </c>
       <c r="R27" t="n">
-        <v>7017015</v>
+        <v>7017016</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4253,7 +4262,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4274,26 +4283,6 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4311,10 +4300,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120277714</v>
+        <v>120272977</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4327,40 +4316,53 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499640</v>
+        <v>499347</v>
       </c>
       <c r="R28" t="n">
-        <v>7016917</v>
+        <v>7017018</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4394,7 +4396,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4403,7 +4405,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4414,27 +4415,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4452,10 +4433,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120278324</v>
+        <v>120277809</v>
       </c>
       <c r="B29" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4468,33 +4449,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -4503,10 +4476,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499536</v>
+        <v>499618</v>
       </c>
       <c r="R29" t="n">
-        <v>7016886</v>
+        <v>7016885</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4543,7 +4516,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4576,9 +4549,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4596,7 +4574,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120273384</v>
+        <v>120278049</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -4631,7 +4609,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4656,13 +4634,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499362</v>
+        <v>499546</v>
       </c>
       <c r="R30" t="n">
-        <v>7017033</v>
+        <v>7016839</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4696,7 +4674,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4716,7 +4694,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4734,10 +4712,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120275779</v>
+        <v>120273613</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4746,41 +4724,58 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499408</v>
+        <v>499334</v>
       </c>
       <c r="R31" t="n">
-        <v>7016909</v>
+        <v>7017033</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4817,7 +4812,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4837,32 +4832,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4880,7 +4850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120272665</v>
+        <v>120273384</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -4915,7 +4885,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4925,7 +4895,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -4940,10 +4910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499381</v>
+        <v>499362</v>
       </c>
       <c r="R32" t="n">
-        <v>7017041</v>
+        <v>7017033</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4980,7 +4950,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5018,7 +4988,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120275167</v>
+        <v>120277525</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -5053,7 +5023,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5063,7 +5033,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -5078,13 +5048,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499357</v>
+        <v>499634</v>
       </c>
       <c r="R33" t="n">
-        <v>7016976</v>
+        <v>7016955</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5118,7 +5088,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5138,7 +5108,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5156,7 +5126,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120273861</v>
+        <v>120276615</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -5191,7 +5161,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5201,7 +5171,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -5216,13 +5186,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499335</v>
+        <v>499484</v>
       </c>
       <c r="R34" t="n">
-        <v>7017016</v>
+        <v>7016963</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5256,7 +5226,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5276,7 +5246,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5294,10 +5264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120278443</v>
+        <v>120275394</v>
       </c>
       <c r="B35" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5310,53 +5280,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499314</v>
+        <v>499319</v>
       </c>
       <c r="R35" t="n">
-        <v>7016944</v>
+        <v>7016956</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5390,7 +5347,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5399,6 +5356,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5409,7 +5367,27 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5427,10 +5405,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120276443</v>
+        <v>120274378</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5439,58 +5417,49 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499460</v>
+        <v>499337</v>
       </c>
       <c r="R36" t="n">
-        <v>7016990</v>
+        <v>7017015</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5527,7 +5496,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5547,7 +5516,27 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5565,10 +5554,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120278049</v>
+        <v>120277714</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5577,58 +5566,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499546</v>
+        <v>499640</v>
       </c>
       <c r="R37" t="n">
-        <v>7016839</v>
+        <v>7016917</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5665,7 +5637,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5686,6 +5658,26 @@
       <c r="AI37" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5703,10 +5695,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120273613</v>
+        <v>120275779</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5715,58 +5707,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499334</v>
+        <v>499408</v>
       </c>
       <c r="R38" t="n">
-        <v>7017033</v>
+        <v>7016909</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5803,7 +5778,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5823,7 +5798,32 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120279007</v>
+        <v>120278994</v>
       </c>
       <c r="B39" t="n">
-        <v>90576</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5853,52 +5853,61 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499409</v>
+        <v>499337</v>
       </c>
       <c r="R39" t="n">
-        <v>7017042</v>
+        <v>7017015</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5932,7 +5941,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5953,26 +5962,6 @@
       <c r="AI39" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5990,10 +5979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120278994</v>
+        <v>120279007</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6002,61 +5991,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499337</v>
+        <v>499409</v>
       </c>
       <c r="R40" t="n">
-        <v>7017015</v>
+        <v>7017042</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6090,7 +6070,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6111,6 +6091,26 @@
       <c r="AI40" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6128,10 +6128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121193255</v>
+        <v>121192442</v>
       </c>
       <c r="B41" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499270</v>
+        <v>499324</v>
       </c>
       <c r="R41" t="n">
-        <v>7017119</v>
+        <v>7017151</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6266,10 +6266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121193691</v>
+        <v>121193255</v>
       </c>
       <c r="B42" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499275</v>
+        <v>499270</v>
       </c>
       <c r="R42" t="n">
-        <v>7017147</v>
+        <v>7017119</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6404,10 +6404,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121192528</v>
+        <v>121194234</v>
       </c>
       <c r="B43" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6416,44 +6416,61 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499324</v>
+        <v>499282</v>
       </c>
       <c r="R43" t="n">
-        <v>7017151</v>
+        <v>7017166</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6487,7 +6504,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6508,26 +6525,6 @@
       <c r="AI43" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6545,10 +6542,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121192442</v>
+        <v>121193691</v>
       </c>
       <c r="B44" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6580,7 +6577,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6605,10 +6602,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499324</v>
+        <v>499275</v>
       </c>
       <c r="R44" t="n">
-        <v>7017151</v>
+        <v>7017147</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6645,7 +6642,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6683,10 +6680,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121194234</v>
+        <v>121192528</v>
       </c>
       <c r="B45" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6695,61 +6692,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499282</v>
+        <v>499324</v>
       </c>
       <c r="R45" t="n">
-        <v>7017166</v>
+        <v>7017151</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6783,7 +6763,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6804,6 +6784,26 @@
       <c r="AI45" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6824,7 +6824,7 @@
         <v>121194426</v>
       </c>
       <c r="B46" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6128,7 +6128,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121192442</v>
+        <v>121193691</v>
       </c>
       <c r="B41" t="n">
         <v>98081</v>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499324</v>
+        <v>499275</v>
       </c>
       <c r="R41" t="n">
-        <v>7017151</v>
+        <v>7017147</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6266,7 +6266,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121193255</v>
+        <v>121192442</v>
       </c>
       <c r="B42" t="n">
         <v>98081</v>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499270</v>
+        <v>499324</v>
       </c>
       <c r="R42" t="n">
-        <v>7017119</v>
+        <v>7017151</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6404,7 +6404,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121194234</v>
+        <v>121193255</v>
       </c>
       <c r="B43" t="n">
         <v>98081</v>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499282</v>
+        <v>499270</v>
       </c>
       <c r="R43" t="n">
-        <v>7017166</v>
+        <v>7017119</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6542,10 +6542,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121193691</v>
+        <v>121192528</v>
       </c>
       <c r="B44" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6554,58 +6554,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499275</v>
+        <v>499324</v>
       </c>
       <c r="R44" t="n">
-        <v>7017147</v>
+        <v>7017151</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6642,7 +6625,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6663,6 +6646,26 @@
       <c r="AI44" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6680,10 +6683,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121192528</v>
+        <v>121194426</v>
       </c>
       <c r="B45" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6692,44 +6695,61 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499324</v>
+        <v>499231</v>
       </c>
       <c r="R45" t="n">
-        <v>7017151</v>
+        <v>7017208</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6763,7 +6783,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6783,27 +6803,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121194426</v>
+        <v>121194234</v>
       </c>
       <c r="B46" t="n">
         <v>98081</v>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499231</v>
+        <v>499282</v>
       </c>
       <c r="R46" t="n">
-        <v>7017208</v>
+        <v>7017166</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6128,10 +6128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121193691</v>
+        <v>121192442</v>
       </c>
       <c r="B41" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499275</v>
+        <v>499324</v>
       </c>
       <c r="R41" t="n">
-        <v>7017147</v>
+        <v>7017151</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6266,10 +6266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121192442</v>
+        <v>121193255</v>
       </c>
       <c r="B42" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499324</v>
+        <v>499270</v>
       </c>
       <c r="R42" t="n">
-        <v>7017151</v>
+        <v>7017119</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6404,10 +6404,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121193255</v>
+        <v>121194234</v>
       </c>
       <c r="B43" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499270</v>
+        <v>499282</v>
       </c>
       <c r="R43" t="n">
-        <v>7017119</v>
+        <v>7017166</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6542,10 +6542,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121192528</v>
+        <v>121194426</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6554,44 +6554,61 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499324</v>
+        <v>499231</v>
       </c>
       <c r="R44" t="n">
-        <v>7017151</v>
+        <v>7017208</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6625,7 +6642,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6645,27 +6662,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6683,10 +6680,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121194426</v>
+        <v>121192528</v>
       </c>
       <c r="B45" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6695,61 +6692,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499231</v>
+        <v>499324</v>
       </c>
       <c r="R45" t="n">
-        <v>7017208</v>
+        <v>7017151</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6783,7 +6763,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6803,7 +6783,27 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121194234</v>
+        <v>121193691</v>
       </c>
       <c r="B46" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6881,13 +6881,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499282</v>
+        <v>499275</v>
       </c>
       <c r="R46" t="n">
-        <v>7017166</v>
+        <v>7017147</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6128,10 +6128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121192442</v>
+        <v>121194426</v>
       </c>
       <c r="B41" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499324</v>
+        <v>499231</v>
       </c>
       <c r="R41" t="n">
-        <v>7017151</v>
+        <v>7017208</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121193255</v>
+        <v>121193691</v>
       </c>
       <c r="B42" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499270</v>
+        <v>499275</v>
       </c>
       <c r="R42" t="n">
-        <v>7017119</v>
+        <v>7017147</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6404,10 +6404,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121194234</v>
+        <v>121192528</v>
       </c>
       <c r="B43" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6416,61 +6416,44 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499282</v>
+        <v>499324</v>
       </c>
       <c r="R43" t="n">
-        <v>7017166</v>
+        <v>7017151</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6504,7 +6487,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6525,6 +6508,26 @@
       <c r="AI43" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6542,10 +6545,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121194426</v>
+        <v>121192442</v>
       </c>
       <c r="B44" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6577,7 +6580,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6602,13 +6605,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499231</v>
+        <v>499324</v>
       </c>
       <c r="R44" t="n">
-        <v>7017208</v>
+        <v>7017151</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6642,7 +6645,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6662,7 +6665,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6680,10 +6683,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121192528</v>
+        <v>121194234</v>
       </c>
       <c r="B45" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6692,44 +6695,61 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499324</v>
+        <v>499282</v>
       </c>
       <c r="R45" t="n">
-        <v>7017151</v>
+        <v>7017166</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6763,7 +6783,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6784,26 +6804,6 @@
       <c r="AI45" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121193691</v>
+        <v>121193255</v>
       </c>
       <c r="B46" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499275</v>
+        <v>499270</v>
       </c>
       <c r="R46" t="n">
-        <v>7017147</v>
+        <v>7017119</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6128,10 +6128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121194426</v>
+        <v>121193691</v>
       </c>
       <c r="B41" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499231</v>
+        <v>499275</v>
       </c>
       <c r="R41" t="n">
-        <v>7017208</v>
+        <v>7017147</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121193691</v>
+        <v>121193255</v>
       </c>
       <c r="B42" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499275</v>
+        <v>499270</v>
       </c>
       <c r="R42" t="n">
-        <v>7017147</v>
+        <v>7017119</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6407,7 +6407,7 @@
         <v>121192528</v>
       </c>
       <c r="B43" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>121192442</v>
       </c>
       <c r="B44" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6683,10 +6683,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121194234</v>
+        <v>121194426</v>
       </c>
       <c r="B45" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499282</v>
+        <v>499231</v>
       </c>
       <c r="R45" t="n">
-        <v>7017166</v>
+        <v>7017208</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121193255</v>
+        <v>121194234</v>
       </c>
       <c r="B46" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6881,13 +6881,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499270</v>
+        <v>499282</v>
       </c>
       <c r="R46" t="n">
-        <v>7017119</v>
+        <v>7017166</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6128,7 +6128,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121193691</v>
+        <v>121193255</v>
       </c>
       <c r="B41" t="n">
         <v>98098</v>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499275</v>
+        <v>499270</v>
       </c>
       <c r="R41" t="n">
-        <v>7017147</v>
+        <v>7017119</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6266,7 +6266,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121193255</v>
+        <v>121193691</v>
       </c>
       <c r="B42" t="n">
         <v>98098</v>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499270</v>
+        <v>499275</v>
       </c>
       <c r="R42" t="n">
-        <v>7017119</v>
+        <v>7017147</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6404,10 +6404,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121192528</v>
+        <v>121192442</v>
       </c>
       <c r="B43" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6416,31 +6416,48 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
@@ -6487,7 +6504,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6508,26 +6525,6 @@
       <c r="AI43" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6545,7 +6542,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121192442</v>
+        <v>121194426</v>
       </c>
       <c r="B44" t="n">
         <v>98098</v>
@@ -6580,7 +6577,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6605,13 +6602,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499324</v>
+        <v>499231</v>
       </c>
       <c r="R44" t="n">
-        <v>7017151</v>
+        <v>7017208</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6645,7 +6642,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6665,7 +6662,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6683,7 +6680,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121194426</v>
+        <v>121194234</v>
       </c>
       <c r="B45" t="n">
         <v>98098</v>
@@ -6718,7 +6715,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6743,10 +6740,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499231</v>
+        <v>499282</v>
       </c>
       <c r="R45" t="n">
-        <v>7017208</v>
+        <v>7017166</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6783,7 +6780,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6803,7 +6800,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6821,10 +6818,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121194234</v>
+        <v>121192528</v>
       </c>
       <c r="B46" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6833,61 +6830,44 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499282</v>
+        <v>499324</v>
       </c>
       <c r="R46" t="n">
-        <v>7017166</v>
+        <v>7017151</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6921,7 +6901,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6942,6 +6922,26 @@
       <c r="AI46" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6128,10 +6128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121193255</v>
+        <v>121193691</v>
       </c>
       <c r="B41" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499270</v>
+        <v>499275</v>
       </c>
       <c r="R41" t="n">
-        <v>7017119</v>
+        <v>7017147</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6266,10 +6266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121193691</v>
+        <v>121194234</v>
       </c>
       <c r="B42" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6326,13 +6326,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499275</v>
+        <v>499282</v>
       </c>
       <c r="R42" t="n">
-        <v>7017147</v>
+        <v>7017166</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6407,7 +6407,7 @@
         <v>121192442</v>
       </c>
       <c r="B43" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>121194426</v>
       </c>
       <c r="B44" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121194234</v>
+        <v>121193255</v>
       </c>
       <c r="B45" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6740,13 +6740,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499282</v>
+        <v>499270</v>
       </c>
       <c r="R45" t="n">
-        <v>7017166</v>
+        <v>7017119</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6821,7 +6821,7 @@
         <v>121192528</v>
       </c>
       <c r="B46" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6128,10 +6128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121193691</v>
+        <v>121193255</v>
       </c>
       <c r="B41" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499275</v>
+        <v>499270</v>
       </c>
       <c r="R41" t="n">
-        <v>7017147</v>
+        <v>7017119</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6269,7 +6269,7 @@
         <v>121194234</v>
       </c>
       <c r="B42" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121192442</v>
+        <v>121193691</v>
       </c>
       <c r="B43" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499324</v>
+        <v>499275</v>
       </c>
       <c r="R43" t="n">
-        <v>7017151</v>
+        <v>7017147</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6542,10 +6542,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121194426</v>
+        <v>121192442</v>
       </c>
       <c r="B44" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6602,13 +6602,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499231</v>
+        <v>499324</v>
       </c>
       <c r="R44" t="n">
-        <v>7017208</v>
+        <v>7017151</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6680,10 +6680,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121193255</v>
+        <v>121192528</v>
       </c>
       <c r="B45" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6692,58 +6692,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499270</v>
+        <v>499324</v>
       </c>
       <c r="R45" t="n">
-        <v>7017119</v>
+        <v>7017151</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6780,7 +6763,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6801,6 +6784,26 @@
       <c r="AI45" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6818,10 +6821,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121192528</v>
+        <v>121194426</v>
       </c>
       <c r="B46" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6830,44 +6833,61 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499324</v>
+        <v>499231</v>
       </c>
       <c r="R46" t="n">
-        <v>7017151</v>
+        <v>7017208</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6901,7 +6921,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6921,27 +6941,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6959,10 +6959,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124508243</v>
+        <v>124508195</v>
       </c>
       <c r="B47" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6971,40 +6971,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7013,13 +7004,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499605</v>
+        <v>499594</v>
       </c>
       <c r="R47" t="n">
-        <v>7016796</v>
+        <v>7016790</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7048,7 +7039,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7058,7 +7049,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7073,6 +7069,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7090,10 +7106,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124508195</v>
+        <v>124510250</v>
       </c>
       <c r="B48" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7106,27 +7122,32 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7135,13 +7156,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499594</v>
+        <v>499689</v>
       </c>
       <c r="R48" t="n">
-        <v>7016790</v>
+        <v>7016946</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7170,7 +7191,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7180,12 +7201,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7199,7 +7220,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -7214,12 +7235,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7237,7 +7258,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124511642</v>
+        <v>124508243</v>
       </c>
       <c r="B49" t="n">
         <v>57883</v>
@@ -7285,24 +7306,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499495</v>
+        <v>499605</v>
       </c>
       <c r="R49" t="n">
-        <v>7016934</v>
+        <v>7016796</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7331,7 +7347,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7341,7 +7357,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7373,10 +7389,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124510250</v>
+        <v>124511642</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7385,20 +7401,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7406,10 +7422,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7423,13 +7448,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499689</v>
+        <v>499495</v>
       </c>
       <c r="R50" t="n">
-        <v>7016946</v>
+        <v>7016934</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7458,7 +7483,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7468,12 +7493,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:07</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7487,27 +7507,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124509973</v>
+        <v>124509586</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -7561,7 +7561,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7575,13 +7575,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499670</v>
+        <v>499669</v>
       </c>
       <c r="R51" t="n">
         <v>7016915</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7677,10 +7677,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124508038</v>
+        <v>124512397</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7689,40 +7689,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7731,13 +7729,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499608</v>
+        <v>499437</v>
       </c>
       <c r="R52" t="n">
-        <v>7016784</v>
+        <v>7016890</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7766,7 +7764,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7776,12 +7774,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7796,6 +7794,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7813,7 +7831,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124509586</v>
+        <v>124512733</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -7847,9 +7865,11 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7863,13 +7883,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499669</v>
+        <v>499409</v>
       </c>
       <c r="R53" t="n">
-        <v>7016915</v>
+        <v>7016902</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7898,7 +7918,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7908,12 +7928,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7965,7 +7985,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124511068</v>
+        <v>124508038</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -8000,7 +8020,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -8013,24 +8033,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499529</v>
+        <v>499608</v>
       </c>
       <c r="R54" t="n">
-        <v>7016877</v>
+        <v>7016784</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8059,7 +8074,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8069,12 +8084,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8106,10 +8121,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124512397</v>
+        <v>124511612</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8118,35 +8133,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8158,10 +8181,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499437</v>
+        <v>499500</v>
       </c>
       <c r="R55" t="n">
-        <v>7016890</v>
+        <v>7016899</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -8193,7 +8216,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8203,12 +8226,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8217,32 +8240,13 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8260,10 +8264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124512733</v>
+        <v>124508624</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8272,38 +8276,40 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -8312,13 +8318,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499409</v>
+        <v>499615</v>
       </c>
       <c r="R56" t="n">
-        <v>7016902</v>
+        <v>7016828</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8347,7 +8353,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8357,12 +8363,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8377,26 +8383,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8566,7 +8552,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124508624</v>
+        <v>124511068</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8601,7 +8587,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8614,16 +8600,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499615</v>
+        <v>499529</v>
       </c>
       <c r="R58" t="n">
-        <v>7016828</v>
+        <v>7016877</v>
       </c>
       <c r="S58" t="n">
         <v>8</v>
@@ -8655,7 +8646,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8665,12 +8656,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8702,10 +8693,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124511612</v>
+        <v>124509973</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8714,43 +8705,33 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8762,10 +8743,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499500</v>
+        <v>499670</v>
       </c>
       <c r="R59" t="n">
-        <v>7016899</v>
+        <v>7016915</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -8797,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8807,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8821,13 +8802,32 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6959,10 +6959,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124508195</v>
+        <v>124511642</v>
       </c>
       <c r="B47" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6971,31 +6971,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7004,13 +7018,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499594</v>
+        <v>499495</v>
       </c>
       <c r="R47" t="n">
-        <v>7016790</v>
+        <v>7016934</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7039,7 +7053,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7049,12 +7063,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7069,26 +7078,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7389,10 +7378,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124511642</v>
+        <v>124508195</v>
       </c>
       <c r="B50" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7401,45 +7390,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7448,13 +7423,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499495</v>
+        <v>499594</v>
       </c>
       <c r="R50" t="n">
-        <v>7016934</v>
+        <v>7016790</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7483,7 +7458,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7493,7 +7468,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7508,6 +7488,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7525,10 +7525,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124509586</v>
+        <v>124511612</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7537,33 +7537,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7575,13 +7585,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499669</v>
+        <v>499500</v>
       </c>
       <c r="R51" t="n">
-        <v>7016915</v>
+        <v>7016899</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7610,7 +7620,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7620,12 +7630,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7634,32 +7644,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7677,7 +7668,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124512397</v>
+        <v>124510139</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -7711,8 +7702,6 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7729,13 +7718,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499437</v>
+        <v>499682</v>
       </c>
       <c r="R52" t="n">
-        <v>7016890</v>
+        <v>7016943</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7764,7 +7753,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7774,12 +7763,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7831,7 +7820,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124512733</v>
+        <v>124512397</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -7883,10 +7872,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499409</v>
+        <v>499437</v>
       </c>
       <c r="R53" t="n">
-        <v>7016902</v>
+        <v>7016890</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -7918,7 +7907,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7928,12 +7917,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7985,10 +7974,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124508038</v>
+        <v>124512733</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7997,40 +7986,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -8039,13 +8026,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499608</v>
+        <v>499409</v>
       </c>
       <c r="R54" t="n">
-        <v>7016784</v>
+        <v>7016902</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8074,7 +8061,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8084,12 +8071,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8104,6 +8091,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8121,10 +8128,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124511612</v>
+        <v>124509973</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8133,43 +8140,33 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8181,10 +8178,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499500</v>
+        <v>499670</v>
       </c>
       <c r="R55" t="n">
-        <v>7016899</v>
+        <v>7016915</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -8216,7 +8213,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8226,12 +8223,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8240,13 +8237,32 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8264,7 +8280,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124508624</v>
+        <v>124511068</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -8299,7 +8315,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8312,16 +8328,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499615</v>
+        <v>499529</v>
       </c>
       <c r="R56" t="n">
-        <v>7016828</v>
+        <v>7016877</v>
       </c>
       <c r="S56" t="n">
         <v>8</v>
@@ -8353,7 +8374,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8363,12 +8384,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8400,10 +8421,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124510139</v>
+        <v>124508624</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8412,36 +8433,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8450,13 +8475,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499682</v>
+        <v>499615</v>
       </c>
       <c r="R57" t="n">
-        <v>7016943</v>
+        <v>7016828</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8485,7 +8510,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8495,12 +8520,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8515,26 +8540,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8552,7 +8557,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124511068</v>
+        <v>124508038</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8587,7 +8592,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8600,24 +8605,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499529</v>
+        <v>499608</v>
       </c>
       <c r="R58" t="n">
-        <v>7016877</v>
+        <v>7016784</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,7 +8693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124509973</v>
+        <v>124509586</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8729,7 +8729,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499670</v>
+        <v>499669</v>
       </c>
       <c r="R59" t="n">
         <v>7016915</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7095,10 +7095,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124510250</v>
+        <v>124508195</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7111,32 +7111,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7145,13 +7140,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499689</v>
+        <v>499594</v>
       </c>
       <c r="R48" t="n">
-        <v>7016946</v>
+        <v>7016790</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7180,7 +7175,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7190,12 +7185,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7209,7 +7204,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -7224,12 +7219,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7247,10 +7242,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124508243</v>
+        <v>124510250</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7259,20 +7254,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7280,19 +7275,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7301,10 +7292,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499605</v>
+        <v>499689</v>
       </c>
       <c r="R49" t="n">
-        <v>7016796</v>
+        <v>7016946</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -7336,7 +7327,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7346,7 +7337,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7360,7 +7356,27 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7378,10 +7394,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124508195</v>
+        <v>124508243</v>
       </c>
       <c r="B50" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7390,31 +7406,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7423,13 +7448,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499594</v>
+        <v>499605</v>
       </c>
       <c r="R50" t="n">
-        <v>7016790</v>
+        <v>7016796</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7458,7 +7483,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7468,12 +7493,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7488,26 +7508,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7668,7 +7668,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124510139</v>
+        <v>124509973</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -7718,13 +7718,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499682</v>
+        <v>499670</v>
       </c>
       <c r="R52" t="n">
-        <v>7016943</v>
+        <v>7016915</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7974,7 +7974,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124512733</v>
+        <v>124510139</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -8008,8 +8008,6 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8026,13 +8024,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499409</v>
+        <v>499682</v>
       </c>
       <c r="R54" t="n">
-        <v>7016902</v>
+        <v>7016943</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8061,7 +8059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8071,12 +8069,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8128,7 +8126,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124509973</v>
+        <v>124509586</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8164,7 +8162,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8178,13 +8176,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499670</v>
+        <v>499669</v>
       </c>
       <c r="R55" t="n">
         <v>7016915</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8213,7 +8211,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8223,12 +8221,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8280,7 +8278,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124511068</v>
+        <v>124508038</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -8315,7 +8313,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8328,24 +8326,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499529</v>
+        <v>499608</v>
       </c>
       <c r="R56" t="n">
-        <v>7016877</v>
+        <v>7016784</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8374,7 +8367,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8384,12 +8377,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8421,10 +8414,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124508624</v>
+        <v>124512733</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8433,40 +8426,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8475,13 +8466,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499615</v>
+        <v>499409</v>
       </c>
       <c r="R57" t="n">
-        <v>7016828</v>
+        <v>7016902</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8510,7 +8501,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8520,12 +8511,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8540,6 +8531,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8557,7 +8568,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124508038</v>
+        <v>124511068</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8592,7 +8603,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8605,19 +8616,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499608</v>
+        <v>499529</v>
       </c>
       <c r="R58" t="n">
-        <v>7016784</v>
+        <v>7016877</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8646,7 +8662,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8656,12 +8672,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,10 +8709,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124509586</v>
+        <v>124508624</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8705,36 +8721,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8743,13 +8763,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499669</v>
+        <v>499615</v>
       </c>
       <c r="R59" t="n">
-        <v>7016915</v>
+        <v>7016828</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8798,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8808,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8808,26 +8828,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6959,10 +6959,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124511642</v>
+        <v>124508195</v>
       </c>
       <c r="B47" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6971,45 +6971,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7018,13 +7004,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499495</v>
+        <v>499594</v>
       </c>
       <c r="R47" t="n">
-        <v>7016934</v>
+        <v>7016790</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7053,7 +7039,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7063,7 +7049,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7078,6 +7069,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7095,10 +7106,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124508195</v>
+        <v>124508243</v>
       </c>
       <c r="B48" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7107,31 +7118,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7140,13 +7160,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499594</v>
+        <v>499605</v>
       </c>
       <c r="R48" t="n">
-        <v>7016790</v>
+        <v>7016796</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7175,7 +7195,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7185,12 +7205,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7205,26 +7220,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7242,10 +7237,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124510250</v>
+        <v>124511642</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7254,20 +7249,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7275,10 +7270,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7292,13 +7296,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499689</v>
+        <v>499495</v>
       </c>
       <c r="R49" t="n">
-        <v>7016946</v>
+        <v>7016934</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7327,7 +7331,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7337,12 +7341,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7356,27 +7355,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7394,10 +7373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124508243</v>
+        <v>124510250</v>
       </c>
       <c r="B50" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7406,20 +7385,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7427,19 +7406,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7448,10 +7423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499605</v>
+        <v>499689</v>
       </c>
       <c r="R50" t="n">
-        <v>7016796</v>
+        <v>7016946</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -7483,7 +7458,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7493,7 +7468,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7507,7 +7487,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7525,10 +7525,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124511612</v>
+        <v>124512733</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7537,43 +7537,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7585,10 +7577,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499500</v>
+        <v>499409</v>
       </c>
       <c r="R51" t="n">
-        <v>7016899</v>
+        <v>7016902</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -7620,7 +7612,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7630,12 +7622,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7644,13 +7636,32 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7668,7 +7679,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124509973</v>
+        <v>124510139</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -7718,13 +7729,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499670</v>
+        <v>499682</v>
       </c>
       <c r="R52" t="n">
-        <v>7016915</v>
+        <v>7016943</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7753,7 +7764,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7763,12 +7774,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7820,7 +7831,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124512397</v>
+        <v>124509586</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -7854,11 +7865,9 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7872,13 +7881,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499437</v>
+        <v>499669</v>
       </c>
       <c r="R53" t="n">
-        <v>7016890</v>
+        <v>7016915</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7907,7 +7916,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7917,12 +7926,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7974,10 +7983,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124510139</v>
+        <v>124511612</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7986,33 +7995,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8024,13 +8043,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499682</v>
+        <v>499500</v>
       </c>
       <c r="R54" t="n">
-        <v>7016943</v>
+        <v>7016899</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8059,7 +8078,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8069,12 +8088,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8083,32 +8102,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124509586</v>
+        <v>124512397</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8160,9 +8160,11 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8176,13 +8178,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499669</v>
+        <v>499437</v>
       </c>
       <c r="R55" t="n">
-        <v>7016915</v>
+        <v>7016890</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8211,7 +8213,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8221,12 +8223,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8278,7 +8280,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124508038</v>
+        <v>124511068</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -8313,7 +8315,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8326,19 +8328,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499608</v>
+        <v>499529</v>
       </c>
       <c r="R56" t="n">
-        <v>7016784</v>
+        <v>7016877</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8367,7 +8374,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8377,12 +8384,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8414,10 +8421,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124512733</v>
+        <v>124508624</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8426,38 +8433,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8466,13 +8475,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499409</v>
+        <v>499615</v>
       </c>
       <c r="R57" t="n">
-        <v>7016902</v>
+        <v>7016828</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8501,7 +8510,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8511,12 +8520,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8531,26 +8540,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8568,7 +8557,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124511068</v>
+        <v>124508038</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8603,7 +8592,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8616,24 +8605,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499529</v>
+        <v>499608</v>
       </c>
       <c r="R58" t="n">
-        <v>7016877</v>
+        <v>7016784</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8662,7 +8646,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8672,12 +8656,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8709,10 +8693,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124508624</v>
+        <v>124509973</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8721,40 +8705,36 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8763,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499615</v>
+        <v>499670</v>
       </c>
       <c r="R59" t="n">
-        <v>7016828</v>
+        <v>7016915</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8798,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8808,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8828,6 +8808,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7106,10 +7106,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124508243</v>
+        <v>124510250</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7118,20 +7118,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7139,19 +7139,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7160,10 +7156,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499605</v>
+        <v>499689</v>
       </c>
       <c r="R48" t="n">
-        <v>7016796</v>
+        <v>7016946</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -7195,7 +7191,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7205,7 +7201,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7219,7 +7220,27 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7237,7 +7258,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124511642</v>
+        <v>124508243</v>
       </c>
       <c r="B49" t="n">
         <v>57883</v>
@@ -7285,24 +7306,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499495</v>
+        <v>499605</v>
       </c>
       <c r="R49" t="n">
-        <v>7016934</v>
+        <v>7016796</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7331,7 +7347,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7341,7 +7357,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7373,10 +7389,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124510250</v>
+        <v>124511642</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7385,20 +7401,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7406,10 +7422,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7423,13 +7448,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499689</v>
+        <v>499495</v>
       </c>
       <c r="R50" t="n">
-        <v>7016946</v>
+        <v>7016934</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7458,7 +7483,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7468,12 +7493,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:07</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7487,27 +7507,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124512733</v>
+        <v>124509973</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -7559,8 +7559,6 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7577,10 +7575,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499409</v>
+        <v>499670</v>
       </c>
       <c r="R51" t="n">
-        <v>7016902</v>
+        <v>7016915</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -7612,7 +7610,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7622,12 +7620,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7679,7 +7677,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124510139</v>
+        <v>124509586</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -7715,7 +7713,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7729,13 +7727,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499682</v>
+        <v>499669</v>
       </c>
       <c r="R52" t="n">
-        <v>7016943</v>
+        <v>7016915</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7764,7 +7762,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7774,12 +7772,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7831,10 +7829,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124509586</v>
+        <v>124508038</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7843,36 +7841,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7881,10 +7883,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499669</v>
+        <v>499608</v>
       </c>
       <c r="R53" t="n">
-        <v>7016915</v>
+        <v>7016784</v>
       </c>
       <c r="S53" t="n">
         <v>7</v>
@@ -7916,7 +7918,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7926,12 +7928,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7946,26 +7948,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8280,10 +8262,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124511068</v>
+        <v>124512733</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8292,40 +8274,33 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8339,13 +8314,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499529</v>
+        <v>499409</v>
       </c>
       <c r="R56" t="n">
-        <v>7016877</v>
+        <v>7016902</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8374,7 +8349,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8384,12 +8359,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8404,6 +8379,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8421,7 +8416,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124508624</v>
+        <v>124511068</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -8456,7 +8451,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8469,16 +8464,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499615</v>
+        <v>499529</v>
       </c>
       <c r="R57" t="n">
-        <v>7016828</v>
+        <v>7016877</v>
       </c>
       <c r="S57" t="n">
         <v>8</v>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8557,7 +8557,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124508038</v>
+        <v>124508624</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8611,13 +8611,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499608</v>
+        <v>499615</v>
       </c>
       <c r="R58" t="n">
-        <v>7016784</v>
+        <v>7016828</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,7 +8693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124509973</v>
+        <v>124510139</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499670</v>
+        <v>499682</v>
       </c>
       <c r="R59" t="n">
-        <v>7016915</v>
+        <v>7016943</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7106,32 +7106,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124510250</v>
+        <v>124511642</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7139,10 +7139,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7156,13 +7165,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499689</v>
+        <v>499495</v>
       </c>
       <c r="R48" t="n">
-        <v>7016946</v>
+        <v>7016934</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7191,7 +7200,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7201,12 +7210,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7220,27 +7224,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7389,10 +7373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124511642</v>
+        <v>124508624</v>
       </c>
       <c r="B50" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7401,45 +7385,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7448,13 +7427,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499495</v>
+        <v>499615</v>
       </c>
       <c r="R50" t="n">
-        <v>7016934</v>
+        <v>7016828</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7483,7 +7462,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7493,7 +7472,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7507,7 +7491,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7525,48 +7509,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124509973</v>
+        <v>124508038</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7575,13 +7563,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499670</v>
+        <v>499608</v>
       </c>
       <c r="R51" t="n">
-        <v>7016915</v>
+        <v>7016784</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7610,7 +7598,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7620,12 +7608,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7640,26 +7628,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7677,43 +7645,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124509586</v>
+        <v>124511068</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7727,13 +7704,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499669</v>
+        <v>499529</v>
       </c>
       <c r="R52" t="n">
-        <v>7016915</v>
+        <v>7016877</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7762,7 +7739,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7772,12 +7749,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7792,26 +7769,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7829,7 +7786,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124508038</v>
+        <v>124511612</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7864,7 +7821,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7877,19 +7834,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499608</v>
+        <v>499500</v>
       </c>
       <c r="R53" t="n">
-        <v>7016784</v>
+        <v>7016899</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7918,7 +7881,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7928,12 +7891,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7942,12 +7905,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7965,55 +7929,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124511612</v>
+        <v>124510250</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8025,10 +7979,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499500</v>
+        <v>499689</v>
       </c>
       <c r="R54" t="n">
-        <v>7016899</v>
+        <v>7016946</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8060,7 +8014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8070,12 +8024,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8084,13 +8038,32 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8108,7 +8081,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124512397</v>
+        <v>124509586</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8142,11 +8115,9 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8160,13 +8131,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499437</v>
+        <v>499669</v>
       </c>
       <c r="R55" t="n">
-        <v>7016890</v>
+        <v>7016915</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8195,7 +8166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8205,12 +8176,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8262,7 +8233,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124512733</v>
+        <v>124509973</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -8296,8 +8267,6 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8314,10 +8283,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499409</v>
+        <v>499670</v>
       </c>
       <c r="R56" t="n">
-        <v>7016902</v>
+        <v>7016915</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -8349,7 +8318,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8359,12 +8328,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8416,52 +8385,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124511068</v>
+        <v>124512397</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8475,13 +8437,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499529</v>
+        <v>499437</v>
       </c>
       <c r="R57" t="n">
-        <v>7016877</v>
+        <v>7016890</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8510,7 +8472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8520,12 +8482,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8540,6 +8502,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8557,52 +8539,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124508624</v>
+        <v>124510139</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8611,13 +8589,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499615</v>
+        <v>499682</v>
       </c>
       <c r="R58" t="n">
-        <v>7016828</v>
+        <v>7016943</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8646,7 +8624,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8656,12 +8634,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8676,6 +8654,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8693,7 +8691,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124510139</v>
+        <v>124512733</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8727,6 +8725,8 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499682</v>
+        <v>499409</v>
       </c>
       <c r="R59" t="n">
-        <v>7016943</v>
+        <v>7016902</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7373,7 +7373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124508624</v>
+        <v>124508038</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499615</v>
+        <v>499608</v>
       </c>
       <c r="R50" t="n">
-        <v>7016828</v>
+        <v>7016784</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7509,7 +7509,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124508038</v>
+        <v>124511612</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7557,19 +7557,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499608</v>
+        <v>499500</v>
       </c>
       <c r="R51" t="n">
-        <v>7016784</v>
+        <v>7016899</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7598,7 +7604,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7608,12 +7614,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7622,12 +7628,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7645,7 +7652,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124511068</v>
+        <v>124508624</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7680,7 +7687,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7693,21 +7700,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499529</v>
+        <v>499615</v>
       </c>
       <c r="R52" t="n">
-        <v>7016877</v>
+        <v>7016828</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -7739,7 +7741,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7749,12 +7751,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7786,7 +7788,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124511612</v>
+        <v>124511068</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7821,7 +7823,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7834,7 +7836,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7846,13 +7847,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499500</v>
+        <v>499529</v>
       </c>
       <c r="R53" t="n">
-        <v>7016899</v>
+        <v>7016877</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7881,7 +7882,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7891,12 +7892,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7905,13 +7906,12 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124510250</v>
+        <v>124512397</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -7963,6 +7963,8 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7979,10 +7981,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499689</v>
+        <v>499437</v>
       </c>
       <c r="R54" t="n">
-        <v>7016946</v>
+        <v>7016890</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8014,7 +8016,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8024,12 +8026,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8081,7 +8083,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124509586</v>
+        <v>124509973</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8117,7 +8119,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8131,13 +8133,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499669</v>
+        <v>499670</v>
       </c>
       <c r="R55" t="n">
         <v>7016915</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8166,7 +8168,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8176,12 +8178,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8233,7 +8235,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124509973</v>
+        <v>124510139</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -8283,13 +8285,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499670</v>
+        <v>499682</v>
       </c>
       <c r="R56" t="n">
-        <v>7016915</v>
+        <v>7016943</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8318,7 +8320,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8328,12 +8330,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8385,7 +8387,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124512397</v>
+        <v>124509586</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -8419,11 +8421,9 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8437,13 +8437,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499437</v>
+        <v>499669</v>
       </c>
       <c r="R57" t="n">
-        <v>7016890</v>
+        <v>7016915</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8539,7 +8539,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124510139</v>
+        <v>124510250</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499682</v>
+        <v>499689</v>
       </c>
       <c r="R58" t="n">
-        <v>7016943</v>
+        <v>7016946</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7373,7 +7373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124508038</v>
+        <v>124511612</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7421,19 +7421,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499608</v>
+        <v>499500</v>
       </c>
       <c r="R50" t="n">
-        <v>7016784</v>
+        <v>7016899</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7462,7 +7468,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7472,12 +7478,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7486,12 +7492,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7509,7 +7516,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124511612</v>
+        <v>124508624</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7544,7 +7551,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7557,25 +7564,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499500</v>
+        <v>499615</v>
       </c>
       <c r="R51" t="n">
-        <v>7016899</v>
+        <v>7016828</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7604,7 +7605,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7614,12 +7615,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7628,13 +7629,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7652,7 +7652,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124508624</v>
+        <v>124508038</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499615</v>
+        <v>499608</v>
       </c>
       <c r="R52" t="n">
-        <v>7016828</v>
+        <v>7016784</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124512397</v>
+        <v>124509973</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -7963,8 +7963,6 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7981,10 +7979,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499437</v>
+        <v>499670</v>
       </c>
       <c r="R54" t="n">
-        <v>7016890</v>
+        <v>7016915</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8016,7 +8014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8026,12 +8024,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8083,7 +8081,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124509973</v>
+        <v>124512397</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8117,6 +8115,8 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499670</v>
+        <v>499437</v>
       </c>
       <c r="R55" t="n">
-        <v>7016915</v>
+        <v>7016890</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8387,7 +8387,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124509586</v>
+        <v>124512733</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -8421,9 +8421,11 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8437,13 +8439,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499669</v>
+        <v>499409</v>
       </c>
       <c r="R57" t="n">
-        <v>7016915</v>
+        <v>7016902</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8472,7 +8474,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8482,12 +8484,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8691,7 +8693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124512733</v>
+        <v>124509586</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8725,11 +8727,9 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499409</v>
+        <v>499669</v>
       </c>
       <c r="R59" t="n">
-        <v>7016902</v>
+        <v>7016915</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6959,10 +6959,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124508195</v>
+        <v>124511642</v>
       </c>
       <c r="B47" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6971,31 +6971,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7004,13 +7018,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499594</v>
+        <v>499495</v>
       </c>
       <c r="R47" t="n">
-        <v>7016790</v>
+        <v>7016934</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7039,7 +7053,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7049,12 +7063,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7069,26 +7078,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7106,7 +7095,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124511642</v>
+        <v>124508243</v>
       </c>
       <c r="B48" t="n">
         <v>57883</v>
@@ -7154,24 +7143,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499495</v>
+        <v>499605</v>
       </c>
       <c r="R48" t="n">
-        <v>7016934</v>
+        <v>7016796</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7200,7 +7184,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7210,7 +7194,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7242,10 +7226,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124508243</v>
+        <v>124508195</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7254,40 +7238,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7296,13 +7271,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499605</v>
+        <v>499594</v>
       </c>
       <c r="R49" t="n">
-        <v>7016796</v>
+        <v>7016790</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7331,7 +7306,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7341,7 +7316,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7356,6 +7336,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7373,7 +7373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124511612</v>
+        <v>124508038</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7421,25 +7421,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499500</v>
+        <v>499608</v>
       </c>
       <c r="R50" t="n">
-        <v>7016899</v>
+        <v>7016784</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7468,7 +7462,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7478,12 +7472,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7492,13 +7486,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7652,7 +7645,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124508038</v>
+        <v>124511068</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7687,7 +7680,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7700,19 +7693,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499608</v>
+        <v>499529</v>
       </c>
       <c r="R52" t="n">
-        <v>7016784</v>
+        <v>7016877</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7741,7 +7739,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7751,12 +7749,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7788,7 +7786,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124511068</v>
+        <v>124511612</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7823,7 +7821,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7836,6 +7834,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7847,13 +7846,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499529</v>
+        <v>499500</v>
       </c>
       <c r="R53" t="n">
-        <v>7016877</v>
+        <v>7016899</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7882,7 +7881,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7892,12 +7891,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7906,12 +7905,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124509973</v>
+        <v>124512397</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -7963,6 +7963,8 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7979,10 +7981,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499670</v>
+        <v>499437</v>
       </c>
       <c r="R54" t="n">
-        <v>7016915</v>
+        <v>7016890</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8014,7 +8016,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8024,12 +8026,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8081,7 +8083,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124512397</v>
+        <v>124510139</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8115,8 +8117,6 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499437</v>
+        <v>499682</v>
       </c>
       <c r="R55" t="n">
-        <v>7016890</v>
+        <v>7016943</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8235,7 +8235,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124510139</v>
+        <v>124512733</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -8269,6 +8269,8 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8285,13 +8287,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499682</v>
+        <v>499409</v>
       </c>
       <c r="R56" t="n">
-        <v>7016943</v>
+        <v>7016902</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8320,7 +8322,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8330,12 +8332,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8387,7 +8389,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124512733</v>
+        <v>124509973</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -8421,8 +8423,6 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499409</v>
+        <v>499670</v>
       </c>
       <c r="R57" t="n">
-        <v>7016902</v>
+        <v>7016915</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7095,10 +7095,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124508243</v>
+        <v>124508195</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7107,40 +7107,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7149,13 +7140,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499605</v>
+        <v>499594</v>
       </c>
       <c r="R48" t="n">
-        <v>7016796</v>
+        <v>7016790</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7184,7 +7175,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7194,7 +7185,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7209,6 +7205,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7226,10 +7242,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124508195</v>
+        <v>124508243</v>
       </c>
       <c r="B49" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7238,31 +7254,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7271,13 +7296,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499594</v>
+        <v>499605</v>
       </c>
       <c r="R49" t="n">
-        <v>7016790</v>
+        <v>7016796</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7306,7 +7331,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7316,12 +7341,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7336,26 +7356,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7373,7 +7373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124508038</v>
+        <v>124511068</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7421,19 +7421,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499608</v>
+        <v>499529</v>
       </c>
       <c r="R50" t="n">
-        <v>7016784</v>
+        <v>7016877</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7462,7 +7467,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7472,12 +7477,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7509,7 +7514,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124508624</v>
+        <v>124508038</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7544,7 +7549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7563,13 +7568,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499615</v>
+        <v>499608</v>
       </c>
       <c r="R51" t="n">
-        <v>7016828</v>
+        <v>7016784</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7598,7 +7603,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7608,12 +7613,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7645,7 +7650,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124511068</v>
+        <v>124511612</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7680,7 +7685,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7693,6 +7698,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7704,13 +7710,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499529</v>
+        <v>499500</v>
       </c>
       <c r="R52" t="n">
-        <v>7016877</v>
+        <v>7016899</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7739,7 +7745,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7749,12 +7755,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7763,12 +7769,13 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7786,7 +7793,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124511612</v>
+        <v>124508624</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7821,7 +7828,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7834,25 +7841,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499500</v>
+        <v>499615</v>
       </c>
       <c r="R53" t="n">
-        <v>7016899</v>
+        <v>7016828</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7881,7 +7882,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7891,12 +7892,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7905,13 +7906,12 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124512397</v>
+        <v>124512733</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499437</v>
+        <v>499409</v>
       </c>
       <c r="R54" t="n">
-        <v>7016890</v>
+        <v>7016902</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8083,7 +8083,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124510139</v>
+        <v>124512397</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8117,6 +8117,8 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8133,13 +8135,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499682</v>
+        <v>499437</v>
       </c>
       <c r="R55" t="n">
-        <v>7016943</v>
+        <v>7016890</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8168,7 +8170,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8178,12 +8180,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8235,7 +8237,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124512733</v>
+        <v>124509586</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -8269,11 +8271,9 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499409</v>
+        <v>499669</v>
       </c>
       <c r="R56" t="n">
-        <v>7016902</v>
+        <v>7016915</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8389,7 +8389,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124509973</v>
+        <v>124510250</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499670</v>
+        <v>499689</v>
       </c>
       <c r="R57" t="n">
-        <v>7016915</v>
+        <v>7016946</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8541,7 +8541,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124510250</v>
+        <v>124510139</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8591,13 +8591,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499689</v>
+        <v>499682</v>
       </c>
       <c r="R58" t="n">
-        <v>7016946</v>
+        <v>7016943</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,7 +8693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124509586</v>
+        <v>124509973</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8729,7 +8729,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499669</v>
+        <v>499670</v>
       </c>
       <c r="R59" t="n">
         <v>7016915</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7095,10 +7095,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124508195</v>
+        <v>124508243</v>
       </c>
       <c r="B48" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7107,31 +7107,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7140,13 +7149,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499594</v>
+        <v>499605</v>
       </c>
       <c r="R48" t="n">
-        <v>7016790</v>
+        <v>7016796</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7175,7 +7184,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7185,12 +7194,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7205,26 +7209,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7242,10 +7226,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124508243</v>
+        <v>124508195</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7254,40 +7238,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7296,13 +7271,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499605</v>
+        <v>499594</v>
       </c>
       <c r="R49" t="n">
-        <v>7016796</v>
+        <v>7016790</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7331,7 +7306,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7341,7 +7316,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7356,6 +7336,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124508038</v>
+        <v>124508624</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7568,13 +7568,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499608</v>
+        <v>499615</v>
       </c>
       <c r="R51" t="n">
-        <v>7016784</v>
+        <v>7016828</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7650,7 +7650,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124511612</v>
+        <v>124508038</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7698,25 +7698,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499500</v>
+        <v>499608</v>
       </c>
       <c r="R52" t="n">
-        <v>7016899</v>
+        <v>7016784</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7745,7 +7739,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7755,12 +7749,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7769,13 +7763,12 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7793,7 +7786,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124508624</v>
+        <v>124511612</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7828,7 +7821,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7841,19 +7834,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499615</v>
+        <v>499500</v>
       </c>
       <c r="R53" t="n">
-        <v>7016828</v>
+        <v>7016899</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7882,7 +7881,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7892,12 +7891,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7906,12 +7905,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124509586</v>
+        <v>124509973</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -8273,7 +8273,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499669</v>
+        <v>499670</v>
       </c>
       <c r="R56" t="n">
         <v>7016915</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8541,7 +8541,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124510139</v>
+        <v>124509586</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8577,7 +8577,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8591,13 +8591,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499682</v>
+        <v>499669</v>
       </c>
       <c r="R58" t="n">
-        <v>7016943</v>
+        <v>7016915</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,7 +8693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124509973</v>
+        <v>124510139</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499670</v>
+        <v>499682</v>
       </c>
       <c r="R59" t="n">
-        <v>7016915</v>
+        <v>7016943</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6959,7 +6959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124511642</v>
+        <v>124508243</v>
       </c>
       <c r="B47" t="n">
         <v>57883</v>
@@ -7007,24 +7007,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499495</v>
+        <v>499605</v>
       </c>
       <c r="R47" t="n">
-        <v>7016934</v>
+        <v>7016796</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7053,7 +7048,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7063,7 +7058,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7095,10 +7090,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124508243</v>
+        <v>124508195</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7107,40 +7102,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7149,13 +7135,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499605</v>
+        <v>499594</v>
       </c>
       <c r="R48" t="n">
-        <v>7016796</v>
+        <v>7016790</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7184,7 +7170,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7194,7 +7180,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7209,6 +7200,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7226,10 +7237,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124508195</v>
+        <v>124511642</v>
       </c>
       <c r="B49" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7238,31 +7249,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7271,13 +7296,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499594</v>
+        <v>499495</v>
       </c>
       <c r="R49" t="n">
-        <v>7016790</v>
+        <v>7016934</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7306,7 +7331,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7316,12 +7341,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7336,26 +7356,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7373,7 +7373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124511068</v>
+        <v>124508038</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7421,24 +7421,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499529</v>
+        <v>499608</v>
       </c>
       <c r="R50" t="n">
-        <v>7016877</v>
+        <v>7016784</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7467,7 +7462,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7477,12 +7472,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7514,7 +7509,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124508624</v>
+        <v>124511068</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7549,7 +7544,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7562,16 +7557,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499615</v>
+        <v>499529</v>
       </c>
       <c r="R51" t="n">
-        <v>7016828</v>
+        <v>7016877</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7650,7 +7650,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124508038</v>
+        <v>124508624</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7704,13 +7704,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499608</v>
+        <v>499615</v>
       </c>
       <c r="R52" t="n">
-        <v>7016784</v>
+        <v>7016828</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124512733</v>
+        <v>124510139</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -7963,8 +7963,6 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7981,13 +7979,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499409</v>
+        <v>499682</v>
       </c>
       <c r="R54" t="n">
-        <v>7016902</v>
+        <v>7016943</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8016,7 +8014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8026,12 +8024,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8083,7 +8081,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124512397</v>
+        <v>124509586</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8117,11 +8115,9 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8135,13 +8131,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499437</v>
+        <v>499669</v>
       </c>
       <c r="R55" t="n">
-        <v>7016890</v>
+        <v>7016915</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8170,7 +8166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8180,12 +8176,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8237,7 +8233,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124509973</v>
+        <v>124512733</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -8271,6 +8267,8 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8287,10 +8285,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499670</v>
+        <v>499409</v>
       </c>
       <c r="R56" t="n">
-        <v>7016915</v>
+        <v>7016902</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -8322,7 +8320,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8332,12 +8330,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8541,7 +8539,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124509586</v>
+        <v>124512397</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8575,9 +8573,11 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8591,13 +8591,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499669</v>
+        <v>499437</v>
       </c>
       <c r="R58" t="n">
-        <v>7016915</v>
+        <v>7016890</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,7 +8693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124510139</v>
+        <v>124509973</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499682</v>
+        <v>499670</v>
       </c>
       <c r="R59" t="n">
-        <v>7016943</v>
+        <v>7016915</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6959,7 +6959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124508243</v>
+        <v>124511642</v>
       </c>
       <c r="B47" t="n">
         <v>57883</v>
@@ -7007,19 +7007,24 @@
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499605</v>
+        <v>499495</v>
       </c>
       <c r="R47" t="n">
-        <v>7016796</v>
+        <v>7016934</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7048,7 +7053,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7058,7 +7063,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7237,7 +7242,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124511642</v>
+        <v>124508243</v>
       </c>
       <c r="B49" t="n">
         <v>57883</v>
@@ -7285,24 +7290,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499495</v>
+        <v>499605</v>
       </c>
       <c r="R49" t="n">
-        <v>7016934</v>
+        <v>7016796</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7373,7 +7373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124508038</v>
+        <v>124511068</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7421,19 +7421,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499608</v>
+        <v>499529</v>
       </c>
       <c r="R50" t="n">
-        <v>7016784</v>
+        <v>7016877</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7462,7 +7467,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7472,12 +7477,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7509,7 +7514,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124511068</v>
+        <v>124508038</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7544,7 +7549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7557,24 +7562,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499529</v>
+        <v>499608</v>
       </c>
       <c r="R51" t="n">
-        <v>7016877</v>
+        <v>7016784</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7650,7 +7650,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124508624</v>
+        <v>124511612</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7698,19 +7698,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499615</v>
+        <v>499500</v>
       </c>
       <c r="R52" t="n">
-        <v>7016828</v>
+        <v>7016899</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7739,7 +7745,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7749,12 +7755,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7763,12 +7769,13 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7786,7 +7793,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124511612</v>
+        <v>124508624</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7821,7 +7828,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7834,25 +7841,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499500</v>
+        <v>499615</v>
       </c>
       <c r="R53" t="n">
-        <v>7016899</v>
+        <v>7016828</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7881,7 +7882,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7891,12 +7892,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7905,13 +7906,12 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124510139</v>
+        <v>124512397</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -7963,6 +7963,8 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7979,13 +7981,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499682</v>
+        <v>499437</v>
       </c>
       <c r="R54" t="n">
-        <v>7016943</v>
+        <v>7016890</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8014,7 +8016,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8024,12 +8026,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8081,7 +8083,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124509586</v>
+        <v>124509973</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8117,7 +8119,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8131,13 +8133,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499669</v>
+        <v>499670</v>
       </c>
       <c r="R55" t="n">
         <v>7016915</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8166,7 +8168,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8176,12 +8178,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8233,7 +8235,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124512733</v>
+        <v>124510139</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -8267,8 +8269,6 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8285,13 +8285,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499409</v>
+        <v>499682</v>
       </c>
       <c r="R56" t="n">
-        <v>7016902</v>
+        <v>7016943</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8387,7 +8387,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124510250</v>
+        <v>124512733</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -8421,6 +8421,8 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8437,10 +8439,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499689</v>
+        <v>499409</v>
       </c>
       <c r="R57" t="n">
-        <v>7016946</v>
+        <v>7016902</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -8472,7 +8474,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8482,12 +8484,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8539,7 +8541,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124512397</v>
+        <v>124510250</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8573,8 +8575,6 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499437</v>
+        <v>499689</v>
       </c>
       <c r="R58" t="n">
-        <v>7016890</v>
+        <v>7016946</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,7 +8693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124509973</v>
+        <v>124509586</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8729,7 +8729,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499670</v>
+        <v>499669</v>
       </c>
       <c r="R59" t="n">
         <v>7016915</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6959,7 +6959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124511642</v>
+        <v>124508243</v>
       </c>
       <c r="B47" t="n">
         <v>57883</v>
@@ -7007,24 +7007,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499495</v>
+        <v>499605</v>
       </c>
       <c r="R47" t="n">
-        <v>7016934</v>
+        <v>7016796</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7053,7 +7048,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7063,7 +7058,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7095,10 +7090,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124508195</v>
+        <v>124511642</v>
       </c>
       <c r="B48" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7107,31 +7102,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7140,13 +7149,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499594</v>
+        <v>499495</v>
       </c>
       <c r="R48" t="n">
-        <v>7016790</v>
+        <v>7016934</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7175,7 +7184,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7185,12 +7194,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7205,26 +7209,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7242,10 +7226,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124508243</v>
+        <v>124508195</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7254,40 +7238,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7296,13 +7271,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499605</v>
+        <v>499594</v>
       </c>
       <c r="R49" t="n">
-        <v>7016796</v>
+        <v>7016790</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7331,7 +7306,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7341,7 +7316,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7356,6 +7336,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124508038</v>
+        <v>124508624</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7568,13 +7568,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499608</v>
+        <v>499615</v>
       </c>
       <c r="R51" t="n">
-        <v>7016784</v>
+        <v>7016828</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7793,7 +7793,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124508624</v>
+        <v>124508038</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499615</v>
+        <v>499608</v>
       </c>
       <c r="R53" t="n">
-        <v>7016828</v>
+        <v>7016784</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -6959,10 +6959,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124508243</v>
+        <v>124508195</v>
       </c>
       <c r="B47" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6971,40 +6971,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7013,13 +7004,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499605</v>
+        <v>499594</v>
       </c>
       <c r="R47" t="n">
-        <v>7016796</v>
+        <v>7016790</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7048,7 +7039,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7058,7 +7049,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7073,6 +7069,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7090,7 +7106,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124511642</v>
+        <v>124508243</v>
       </c>
       <c r="B48" t="n">
         <v>57883</v>
@@ -7138,24 +7154,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499495</v>
+        <v>499605</v>
       </c>
       <c r="R48" t="n">
-        <v>7016934</v>
+        <v>7016796</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7184,7 +7195,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7194,7 +7205,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7226,10 +7237,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124508195</v>
+        <v>124511642</v>
       </c>
       <c r="B49" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7238,31 +7249,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7271,13 +7296,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499594</v>
+        <v>499495</v>
       </c>
       <c r="R49" t="n">
-        <v>7016790</v>
+        <v>7016934</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7306,7 +7331,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7316,12 +7341,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7336,26 +7356,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7373,7 +7373,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124511068</v>
+        <v>124508038</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7421,24 +7421,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499529</v>
+        <v>499608</v>
       </c>
       <c r="R50" t="n">
-        <v>7016877</v>
+        <v>7016784</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7467,7 +7462,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7477,12 +7472,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7514,7 +7509,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124508624</v>
+        <v>124511612</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7549,7 +7544,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7562,19 +7557,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499615</v>
+        <v>499500</v>
       </c>
       <c r="R51" t="n">
-        <v>7016828</v>
+        <v>7016899</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7603,7 +7604,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7613,12 +7614,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7627,12 +7628,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7650,7 +7652,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124511612</v>
+        <v>124511068</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7685,7 +7687,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7698,7 +7700,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7710,13 +7711,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499500</v>
+        <v>499529</v>
       </c>
       <c r="R52" t="n">
-        <v>7016899</v>
+        <v>7016877</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7745,7 +7746,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7755,12 +7756,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7769,13 +7770,12 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7793,7 +7793,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124508038</v>
+        <v>124508624</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499608</v>
+        <v>499615</v>
       </c>
       <c r="R53" t="n">
-        <v>7016784</v>
+        <v>7016828</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124512397</v>
+        <v>124510250</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -7963,8 +7963,6 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7981,10 +7979,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499437</v>
+        <v>499689</v>
       </c>
       <c r="R54" t="n">
-        <v>7016890</v>
+        <v>7016946</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8016,7 +8014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8026,12 +8024,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8541,7 +8539,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124510250</v>
+        <v>124509586</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8577,7 +8575,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8591,13 +8589,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499689</v>
+        <v>499669</v>
       </c>
       <c r="R58" t="n">
-        <v>7016946</v>
+        <v>7016915</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8626,7 +8624,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8636,12 +8634,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,7 +8691,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124509586</v>
+        <v>124512397</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8727,9 +8725,11 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499669</v>
+        <v>499437</v>
       </c>
       <c r="R59" t="n">
-        <v>7016915</v>
+        <v>7016890</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124510250</v>
+        <v>124509586</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -7965,7 +7965,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7979,13 +7979,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499689</v>
+        <v>499669</v>
       </c>
       <c r="R54" t="n">
-        <v>7016946</v>
+        <v>7016915</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8081,7 +8081,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124509973</v>
+        <v>124510139</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -8131,13 +8131,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499670</v>
+        <v>499682</v>
       </c>
       <c r="R55" t="n">
-        <v>7016915</v>
+        <v>7016943</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8233,7 +8233,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124510139</v>
+        <v>124510250</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -8283,13 +8283,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499682</v>
+        <v>499689</v>
       </c>
       <c r="R56" t="n">
-        <v>7016943</v>
+        <v>7016946</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8385,7 +8385,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124512733</v>
+        <v>124509973</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -8419,8 +8419,6 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8437,10 +8435,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499409</v>
+        <v>499670</v>
       </c>
       <c r="R57" t="n">
-        <v>7016902</v>
+        <v>7016915</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -8472,7 +8470,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8482,12 +8480,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8539,7 +8537,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124509586</v>
+        <v>124512397</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8573,9 +8571,11 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499669</v>
+        <v>499437</v>
       </c>
       <c r="R58" t="n">
-        <v>7016915</v>
+        <v>7016890</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8691,7 +8691,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124512397</v>
+        <v>124512733</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499437</v>
+        <v>499409</v>
       </c>
       <c r="R59" t="n">
-        <v>7016890</v>
+        <v>7016902</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7929,10 +7929,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124509586</v>
+        <v>124510250</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7979,13 +7979,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499669</v>
+        <v>499689</v>
       </c>
       <c r="R54" t="n">
-        <v>7016915</v>
+        <v>7016946</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8081,10 +8081,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124510139</v>
+        <v>124512397</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8115,6 +8115,8 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8131,13 +8133,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499682</v>
+        <v>499437</v>
       </c>
       <c r="R55" t="n">
-        <v>7016943</v>
+        <v>7016890</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8166,7 +8168,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8176,12 +8178,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8233,10 +8235,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124510250</v>
+        <v>124509586</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8269,7 +8271,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8283,13 +8285,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499689</v>
+        <v>499669</v>
       </c>
       <c r="R56" t="n">
-        <v>7016946</v>
+        <v>7016915</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8318,7 +8320,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8328,12 +8330,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8388,7 +8390,7 @@
         <v>124509973</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8537,10 +8539,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124512397</v>
+        <v>124510139</v>
       </c>
       <c r="B58" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8571,8 +8573,6 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499437</v>
+        <v>499682</v>
       </c>
       <c r="R58" t="n">
-        <v>7016890</v>
+        <v>7016943</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8694,7 +8694,7 @@
         <v>124512733</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7929,7 +7929,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124510250</v>
+        <v>124509973</v>
       </c>
       <c r="B54" t="n">
         <v>57635</v>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499689</v>
+        <v>499670</v>
       </c>
       <c r="R54" t="n">
-        <v>7016946</v>
+        <v>7016915</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8081,7 +8081,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124512397</v>
+        <v>124509586</v>
       </c>
       <c r="B55" t="n">
         <v>57635</v>
@@ -8115,11 +8115,9 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8133,13 +8131,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499437</v>
+        <v>499669</v>
       </c>
       <c r="R55" t="n">
-        <v>7016890</v>
+        <v>7016915</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8168,7 +8166,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8178,12 +8176,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8235,7 +8233,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124509586</v>
+        <v>124512733</v>
       </c>
       <c r="B56" t="n">
         <v>57635</v>
@@ -8269,9 +8267,11 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8285,13 +8285,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499669</v>
+        <v>499409</v>
       </c>
       <c r="R56" t="n">
-        <v>7016915</v>
+        <v>7016902</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8387,7 +8387,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124509973</v>
+        <v>124510250</v>
       </c>
       <c r="B57" t="n">
         <v>57635</v>
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499670</v>
+        <v>499689</v>
       </c>
       <c r="R57" t="n">
-        <v>7016915</v>
+        <v>7016946</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8691,7 +8691,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124512733</v>
+        <v>124512397</v>
       </c>
       <c r="B59" t="n">
         <v>57635</v>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499409</v>
+        <v>499437</v>
       </c>
       <c r="R59" t="n">
-        <v>7016902</v>
+        <v>7016890</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -7929,16 +7929,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124509973</v>
+        <v>124512733</v>
       </c>
       <c r="B54" t="n">
         <v>57635</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7963,6 +7958,8 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -7979,10 +7976,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499670</v>
+        <v>499409</v>
       </c>
       <c r="R54" t="n">
-        <v>7016915</v>
+        <v>7016902</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8014,7 +8011,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8024,12 +8021,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8081,16 +8078,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124509586</v>
+        <v>124510250</v>
       </c>
       <c r="B55" t="n">
         <v>57635</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8117,7 +8109,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8131,13 +8123,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499669</v>
+        <v>499689</v>
       </c>
       <c r="R55" t="n">
-        <v>7016915</v>
+        <v>7016946</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8166,7 +8158,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8176,12 +8168,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8233,16 +8225,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124512733</v>
+        <v>124509973</v>
       </c>
       <c r="B56" t="n">
         <v>57635</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8267,8 +8254,6 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -8285,10 +8270,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499409</v>
+        <v>499670</v>
       </c>
       <c r="R56" t="n">
-        <v>7016902</v>
+        <v>7016915</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -8320,7 +8305,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8330,12 +8315,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8387,16 +8372,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124510250</v>
+        <v>124510139</v>
       </c>
       <c r="B57" t="n">
         <v>57635</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8437,13 +8417,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499689</v>
+        <v>499682</v>
       </c>
       <c r="R57" t="n">
-        <v>7016946</v>
+        <v>7016943</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8472,7 +8452,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8482,12 +8462,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8539,16 +8519,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124510139</v>
+        <v>124509586</v>
       </c>
       <c r="B58" t="n">
         <v>57635</v>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8575,7 +8550,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8589,13 +8564,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499682</v>
+        <v>499669</v>
       </c>
       <c r="R58" t="n">
-        <v>7016943</v>
+        <v>7016915</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8624,7 +8599,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8634,12 +8609,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8695,11 +8670,6 @@
       </c>
       <c r="B59" t="n">
         <v>57635</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,73 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118982021</v>
+        <v>120277408</v>
       </c>
       <c r="B2" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499371</v>
+        <v>499566</v>
       </c>
       <c r="R2" t="n">
-        <v>7017042</v>
+        <v>7016949</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,17 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 16 st skott/stjälkar inom 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +781,27 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,70 +819,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118981029</v>
+        <v>120278324</v>
       </c>
       <c r="B3" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499309</v>
+        <v>499536</v>
       </c>
       <c r="R3" t="n">
-        <v>7017233</v>
+        <v>7016886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,17 +895,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 19 st skott/stjälkar inom ca 5 m2 yta. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,7 +925,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,73 +958,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118981871</v>
+        <v>120279007</v>
       </c>
       <c r="B4" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499309</v>
+        <v>499409</v>
       </c>
       <c r="R4" t="n">
-        <v>7017130</v>
+        <v>7017042</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1041,17 +1034,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar, 1 st överblommad blomstängel och 1 st vinterståndare inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1064,27 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns liggande och stående död ved. På frisk mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,73 +1102,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118980671</v>
+        <v>124508195</v>
       </c>
       <c r="B5" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499374</v>
+        <v>499594</v>
       </c>
       <c r="R5" t="n">
-        <v>7017134</v>
+        <v>7016790</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1179,17 +1172,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Knärot med minst 9 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,18 +1201,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1227,70 +1244,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118981652</v>
+        <v>120276314</v>
       </c>
       <c r="B6" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499264</v>
+        <v>499419</v>
       </c>
       <c r="R6" t="n">
-        <v>7017222</v>
+        <v>7016971</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1317,17 +1320,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 7 st skott/stjälkar. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,7 +1350,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1365,15 +1388,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118981133</v>
+        <v>118980864</v>
       </c>
       <c r="B7" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,54 +1399,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499309</v>
+        <v>499374</v>
       </c>
       <c r="R7" t="n">
-        <v>7017233</v>
+        <v>7017134</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1465,7 +1466,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Knärot med minst 57 st skott/stjälkar och 4 st överblommade blomstänglar inom ca 5 m2 yta. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ett par bålar av garnlav i äldre granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,7 +1486,27 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Död gren på lenande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1503,70 +1524,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118981456</v>
+        <v>118981709</v>
       </c>
       <c r="B8" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499272</v>
+        <v>499264</v>
       </c>
       <c r="R8" t="n">
-        <v>7017240</v>
+        <v>7017222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1603,7 +1602,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 7 st skott/stjälkar inom ca 3 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxta bålar av garnlav. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1624,6 +1623,31 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Döda grenar på levande träd. # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1641,15 +1665,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118981571</v>
+        <v>120275394</v>
       </c>
       <c r="B9" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,57 +1676,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499264</v>
+        <v>499319</v>
       </c>
       <c r="R9" t="n">
-        <v>7017222</v>
+        <v>7016956</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1731,17 +1733,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1761,7 +1763,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1779,19 +1801,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118980864</v>
+        <v>120275534</v>
       </c>
       <c r="B10" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1812,7 +1829,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1822,10 +1843,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499374</v>
+        <v>499369</v>
       </c>
       <c r="R10" t="n">
-        <v>7017134</v>
+        <v>7016923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1852,17 +1873,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ett par bålar av garnlav i äldre granskog. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1882,7 +1903,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1902,7 +1923,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Död gren på lenande träd. # Picea abies</t>
+          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1920,19 +1941,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118981709</v>
+        <v>120275779</v>
       </c>
       <c r="B11" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1963,10 +1979,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499264</v>
+        <v>499408</v>
       </c>
       <c r="R11" t="n">
-        <v>7017222</v>
+        <v>7016909</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1993,17 +2009,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar av garnlav. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2023,7 +2039,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2048,7 +2064,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Döda grenar på levande träd. # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2066,73 +2082,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118980813</v>
+        <v>120277714</v>
       </c>
       <c r="B12" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499374</v>
+        <v>499640</v>
       </c>
       <c r="R12" t="n">
-        <v>7017134</v>
+        <v>7016917</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2156,17 +2150,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spindelblomster med minst 2 st skott/stjälkar inom ca 1 m2 yta. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2186,7 +2180,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2204,15 +2218,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120273132</v>
+        <v>120277809</v>
       </c>
       <c r="B13" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2220,54 +2229,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499362</v>
+        <v>499618</v>
       </c>
       <c r="R13" t="n">
-        <v>7017047</v>
+        <v>7016885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2304,7 +2296,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2324,7 +2316,27 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2342,15 +2354,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120275167</v>
+        <v>121192528</v>
       </c>
       <c r="B14" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,54 +2365,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499357</v>
+        <v>499324</v>
       </c>
       <c r="R14" t="n">
-        <v>7016976</v>
+        <v>7017151</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2432,17 +2422,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2462,7 +2452,27 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2480,64 +2490,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120276314</v>
+        <v>124506970</v>
       </c>
       <c r="B15" t="n">
-        <v>90630</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499419</v>
+        <v>499591</v>
       </c>
       <c r="R15" t="n">
-        <v>7016971</v>
+        <v>7016763</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2561,17 +2555,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ullticka som här växer resupinat med minst 26 fruktkroppar utbredda på minst 6 meter av en liggande död granstam. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2580,18 +2579,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2606,12 +2599,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Stammen har både markkontakt och är bitvis upplyft ett par dm över marken. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2629,55 +2622,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120276615</v>
+        <v>124509586</v>
       </c>
       <c r="B16" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2685,17 +2663,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499484</v>
+        <v>499669</v>
       </c>
       <c r="R16" t="n">
-        <v>7016963</v>
+        <v>7016915</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2719,17 +2697,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2738,7 +2726,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2747,9 +2734,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2767,15 +2769,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120272977</v>
+        <v>124509973</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2783,33 +2780,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2819,17 +2810,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499347</v>
+        <v>499670</v>
       </c>
       <c r="R17" t="n">
-        <v>7017018</v>
+        <v>7016915</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2853,17 +2844,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2880,9 +2881,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2900,15 +2916,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120275534</v>
+        <v>124510139</v>
       </c>
       <c r="B18" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2916,41 +2927,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499369</v>
+        <v>499682</v>
       </c>
       <c r="R18" t="n">
-        <v>7016923</v>
+        <v>7016943</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2977,17 +2991,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2996,7 +3020,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3005,11 +3028,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3022,12 +3040,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Torra döda grenar nertill på levande gran. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3045,15 +3063,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120278324</v>
+        <v>124510250</v>
       </c>
       <c r="B19" t="n">
-        <v>90626</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3061,48 +3074,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499536</v>
+        <v>499689</v>
       </c>
       <c r="R19" t="n">
-        <v>7016886</v>
+        <v>7016946</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3126,17 +3138,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 8 fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3145,7 +3167,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3154,11 +3175,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3169,9 +3185,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3189,55 +3210,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120276443</v>
+        <v>124512397</v>
       </c>
       <c r="B20" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3245,17 +3253,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499460</v>
+        <v>499437</v>
       </c>
       <c r="R20" t="n">
-        <v>7016990</v>
+        <v>7016890</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3279,17 +3287,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3298,7 +3316,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3307,9 +3324,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3327,55 +3359,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120273861</v>
+        <v>124512733</v>
       </c>
       <c r="B21" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3383,17 +3402,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499335</v>
+        <v>499409</v>
       </c>
       <c r="R21" t="n">
-        <v>7017016</v>
+        <v>7016902</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3417,17 +3436,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3436,7 +3465,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3445,9 +3473,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3465,73 +3508,62 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120273384</v>
+        <v>124508243</v>
       </c>
       <c r="B22" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499362</v>
+        <v>499605</v>
       </c>
       <c r="R22" t="n">
-        <v>7017033</v>
+        <v>7016796</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3555,17 +3587,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3574,18 +3611,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3603,55 +3634,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120273613</v>
+        <v>124511642</v>
       </c>
       <c r="B23" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3659,17 +3684,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499334</v>
+        <v>499495</v>
       </c>
       <c r="R23" t="n">
-        <v>7017033</v>
+        <v>7016934</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3693,17 +3718,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3712,18 +3742,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3741,55 +3765,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120276956</v>
+        <v>120272977</v>
       </c>
       <c r="B24" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3797,17 +3812,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499543</v>
+        <v>499347</v>
       </c>
       <c r="R24" t="n">
-        <v>7016946</v>
+        <v>7017018</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3841,7 +3856,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3850,7 +3865,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3861,7 +3875,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3879,55 +3893,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120277899</v>
+        <v>120278443</v>
       </c>
       <c r="B25" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3935,17 +3940,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499598</v>
+        <v>499314</v>
       </c>
       <c r="R25" t="n">
-        <v>7016864</v>
+        <v>7016944</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3979,7 +3984,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3988,7 +3993,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3999,7 +4003,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4017,15 +4021,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120278049</v>
+        <v>118980671</v>
       </c>
       <c r="B26" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4051,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4077,13 +4076,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499546</v>
+        <v>499374</v>
       </c>
       <c r="R26" t="n">
-        <v>7016839</v>
+        <v>7017134</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4107,17 +4106,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 9 st skott/stjälkar och 3 st överblommade blomstänglar inom ca 1 m2 yta. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4137,7 +4136,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4155,56 +4154,68 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120277714</v>
+        <v>118981133</v>
       </c>
       <c r="B27" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499640</v>
+        <v>499309</v>
       </c>
       <c r="R27" t="n">
-        <v>7016917</v>
+        <v>7017233</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4228,17 +4239,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 57 st skott/stjälkar och 4 st överblommade blomstänglar inom ca 5 m2 yta. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4258,27 +4269,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torr död gren på levande träd. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4296,53 +4287,65 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275779</v>
+        <v>118981571</v>
       </c>
       <c r="B28" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499408</v>
+        <v>499264</v>
       </c>
       <c r="R28" t="n">
-        <v>7016909</v>
+        <v>7017222</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4369,17 +4372,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flertalet exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar. Här finns även spindelblomster. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4399,32 +4402,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4442,15 +4420,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120277525</v>
+        <v>118981871</v>
       </c>
       <c r="B29" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4502,13 +4475,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499634</v>
+        <v>499309</v>
       </c>
       <c r="R29" t="n">
-        <v>7016955</v>
+        <v>7017130</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4532,17 +4505,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar, 1 st överblommad blomstängel och 1 st vinterståndare inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4562,7 +4535,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4580,61 +4553,65 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120274378</v>
+        <v>120272547</v>
       </c>
       <c r="B30" t="n">
-        <v>90648</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499337</v>
+        <v>499399</v>
       </c>
       <c r="R30" t="n">
-        <v>7017015</v>
+        <v>7017051</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4671,7 +4648,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 5 st. fruktkroppar av granticka på en död stående gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4692,26 +4669,6 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4729,56 +4686,68 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120275394</v>
+        <v>120272665</v>
       </c>
       <c r="B31" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499319</v>
+        <v>499381</v>
       </c>
       <c r="R31" t="n">
-        <v>7016956</v>
+        <v>7017041</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4812,7 +4781,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Enstaka exemplar av långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4833,26 +4802,6 @@
       <c r="AI31" t="inlineStr">
         <is>
           <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4870,64 +4819,68 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120277408</v>
+        <v>120273132</v>
       </c>
       <c r="B32" t="n">
-        <v>90626</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499566</v>
+        <v>499362</v>
       </c>
       <c r="R32" t="n">
-        <v>7016949</v>
+        <v>7017047</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4961,7 +4914,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 40 fruktkroppar av harticka på två döda granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 32 st skott/stjälkar och 3 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4981,27 +4934,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # 1 st. högstubbe och 1 st. död hellång gran. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5019,51 +4952,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120278443</v>
+        <v>120273384</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5071,14 +5003,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Fäviken, Lit, Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499314</v>
+        <v>499362</v>
       </c>
       <c r="R33" t="n">
-        <v>7016944</v>
+        <v>7017033</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5115,7 +5047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar och 2 st överblommade blomstänglar med fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5124,6 +5056,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5134,7 +5067,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis måttliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5152,15 +5085,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120272547</v>
+        <v>120273613</v>
       </c>
       <c r="B34" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5187,7 +5115,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5212,13 +5140,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499399</v>
+        <v>499334</v>
       </c>
       <c r="R34" t="n">
-        <v>7017051</v>
+        <v>7017033</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5252,7 +5180,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Knärot med minst 180 st skott/stjälkar och 1 st överblommad blomstängel inom ca 5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 13 st skott/stjälkar och 1 st överblommad blomstängel med fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5290,15 +5218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120275293</v>
+        <v>120273861</v>
       </c>
       <c r="B35" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5325,7 +5248,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5335,7 +5258,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -5350,13 +5273,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499319</v>
+        <v>499335</v>
       </c>
       <c r="R35" t="n">
-        <v>7016956</v>
+        <v>7017016</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5390,7 +5313,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 3 st överblommade blomstänglar/fröställningar inom ca 4 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5410,7 +5333,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5428,56 +5351,68 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120277809</v>
+        <v>120275167</v>
       </c>
       <c r="B36" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499618</v>
+        <v>499357</v>
       </c>
       <c r="R36" t="n">
-        <v>7016885</v>
+        <v>7016976</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5511,7 +5446,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka långväxta exemplar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 8 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5531,27 +5466,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>En mer luckig del av grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5569,37 +5484,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120277582</v>
+        <v>120275293</v>
       </c>
       <c r="B37" t="n">
-        <v>96954</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5609,10 +5519,14 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
@@ -5625,13 +5539,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499634</v>
+        <v>499319</v>
       </c>
       <c r="R37" t="n">
-        <v>7016955</v>
+        <v>7016956</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5665,7 +5579,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 2 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5685,7 +5599,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis större mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5703,15 +5617,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120272665</v>
+        <v>120276443</v>
       </c>
       <c r="B38" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5738,7 +5647,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5763,13 +5672,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499381</v>
+        <v>499460</v>
       </c>
       <c r="R38" t="n">
-        <v>7017041</v>
+        <v>7016990</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5803,7 +5712,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Knärot med minst 23 st skott/stjälkar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 56 st skott/stjälkar inom ca 0,5 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5823,7 +5732,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5841,15 +5750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120278994</v>
+        <v>120276615</v>
       </c>
       <c r="B39" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5876,7 +5780,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5886,7 +5790,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -5901,10 +5805,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499337</v>
+        <v>499484</v>
       </c>
       <c r="R39" t="n">
-        <v>7017015</v>
+        <v>7016963</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5941,7 +5845,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 110 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5961,7 +5865,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5979,61 +5883,65 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120279007</v>
+        <v>120276956</v>
       </c>
       <c r="B40" t="n">
-        <v>90628</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499409</v>
+        <v>499543</v>
       </c>
       <c r="R40" t="n">
-        <v>7017042</v>
+        <v>7016946</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6070,7 +5978,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Tre fruktkroppar av harticka på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 15 st skott/stjälkar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6090,27 +5998,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Troligen döende skadad gran. # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6128,15 +6016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121193255</v>
+        <v>120277439</v>
       </c>
       <c r="B41" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6163,7 +6046,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6173,7 +6056,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -6188,13 +6071,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499270</v>
+        <v>499582</v>
       </c>
       <c r="R41" t="n">
-        <v>7017119</v>
+        <v>7016960</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6218,17 +6101,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6248,7 +6126,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+          <t>Äldre granskog på frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6266,15 +6144,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121194234</v>
+        <v>120277525</v>
       </c>
       <c r="B42" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6301,7 +6174,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6311,7 +6184,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -6326,10 +6199,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499282</v>
+        <v>499634</v>
       </c>
       <c r="R42" t="n">
-        <v>7017166</v>
+        <v>7016955</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6356,17 +6229,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 50 st skott/stjälkar och 1 st överblommad blomstängel/fröställning inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6386,7 +6259,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6404,15 +6277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121193691</v>
+        <v>120277899</v>
       </c>
       <c r="B43" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6439,7 +6307,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6449,7 +6317,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -6464,10 +6332,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499275</v>
+        <v>499598</v>
       </c>
       <c r="R43" t="n">
-        <v>7017147</v>
+        <v>7016864</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6494,17 +6362,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 240 st skott/stjälkar och 30 st överblommade blomstänglar/fröställningar inom ca 2 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6524,7 +6392,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6542,15 +6410,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121192442</v>
+        <v>120278049</v>
       </c>
       <c r="B44" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6577,7 +6440,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6587,7 +6450,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -6602,10 +6465,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499324</v>
+        <v>499546</v>
       </c>
       <c r="R44" t="n">
-        <v>7017151</v>
+        <v>7016839</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6632,17 +6495,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 7 st skott/stjälkar och 1 st överblommad blomstängel med fröställning inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6662,7 +6525,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och myrstackar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6680,53 +6543,65 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121192528</v>
+        <v>120278994</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499324</v>
+        <v>499337</v>
       </c>
       <c r="R45" t="n">
-        <v>7017151</v>
+        <v>7017015</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6753,17 +6628,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 6 st skott/stjälkar och 1 st överblommad blomstängel inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6783,27 +6658,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark. Här finns olikåldriga träd och träd med socklar. Bitvis relativt rikliga mängder liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6821,15 +6676,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121194426</v>
+        <v>121192442</v>
       </c>
       <c r="B46" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6856,7 +6706,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6881,13 +6731,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499231</v>
+        <v>499324</v>
       </c>
       <c r="R46" t="n">
-        <v>7017208</v>
+        <v>7017151</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6921,7 +6771,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+          <t>Knärot med minst 4 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6941,7 +6791,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6959,58 +6809,68 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124508195</v>
+        <v>121193255</v>
       </c>
       <c r="B47" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499594</v>
+        <v>499270</v>
       </c>
       <c r="R47" t="n">
-        <v>7016790</v>
+        <v>7017119</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7034,27 +6894,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>19:09</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>19:09</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Fruktkropparna växer i stambasen av en död stående avbarkad gran med potentiella färska födosökspår efter tretåig hackspett.</t>
+          <t>Knärot med minst 12 st skott/stjälkar och 2 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7063,32 +6913,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7106,67 +6942,68 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124508243</v>
+        <v>121193691</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499605</v>
+        <v>499275</v>
       </c>
       <c r="R48" t="n">
-        <v>7016796</v>
+        <v>7017147</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7190,22 +7027,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>19:13</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>19:13</t>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Knärot med minst 72 st skott/stjälkar och 7 st fröställningar inom ca 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7214,12 +7046,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7237,54 +7075,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124511642</v>
+        <v>121194234</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7292,17 +7126,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499495</v>
+        <v>499282</v>
       </c>
       <c r="R49" t="n">
-        <v>7016934</v>
+        <v>7017166</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7326,22 +7160,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>20:43</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>20:43</t>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Knärot med minst 15 st skott/stjälkar och 6 st fröställningar inom ca 2 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7350,12 +7179,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Här finns träd med socklar och måttliga mängder med liggande och stående död ved. På frisk mark.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7373,15 +7208,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124508038</v>
+        <v>121194426</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7408,32 +7238,38 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499608</v>
+        <v>499231</v>
       </c>
       <c r="R50" t="n">
-        <v>7016784</v>
+        <v>7017208</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7457,27 +7293,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>19:03</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>19:03</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
+          <t>Knärot med minst 3 st skott/stjälkar och 1 st fröställning inom ca 1 m2 yta. P.g.a. snötäcke vid besöket på fyndplatsen kunde endast ett antal av skotten räknas, troligen finns här fler knärotsskott. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7486,12 +7312,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk och rönn. Här finns måttliga mängder med liggande och stående död ved. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7509,15 +7341,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124511612</v>
+        <v>124508038</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7544,7 +7371,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7557,25 +7384,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499500</v>
+        <v>499608</v>
       </c>
       <c r="R51" t="n">
-        <v>7016899</v>
+        <v>7016784</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7604,7 +7425,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7614,12 +7435,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
+          <t>Minst 90 plantor inom ca 3 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7628,13 +7449,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7652,15 +7472,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124511068</v>
+        <v>124508624</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7687,7 +7502,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7700,21 +7515,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499529</v>
+        <v>499615</v>
       </c>
       <c r="R52" t="n">
-        <v>7016877</v>
+        <v>7016828</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -7746,7 +7556,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7756,12 +7566,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
+          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7793,15 +7603,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124508624</v>
+        <v>124511068</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7828,7 +7633,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7841,16 +7646,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499615</v>
+        <v>499529</v>
       </c>
       <c r="R53" t="n">
-        <v>7016828</v>
+        <v>7016877</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -7882,7 +7692,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7892,12 +7702,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 3 x 0,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7929,42 +7739,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124512733</v>
+        <v>124511612</v>
       </c>
       <c r="B54" t="n">
-        <v>57635</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7976,10 +7794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499409</v>
+        <v>499500</v>
       </c>
       <c r="R54" t="n">
-        <v>7016902</v>
+        <v>7016899</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -8011,7 +7829,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8021,12 +7839,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (+ 5 år) men ev. även något färskare ringhack, längs minst 7 meter på en relativt grov gran. Kring fyndplatsen finns en volym av stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 20 plantor inom ca 0, 25 m2.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8035,32 +7853,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8078,40 +7877,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124510250</v>
+        <v>120277582</v>
       </c>
       <c r="B55" t="n">
-        <v>57635</v>
+        <v>97983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8119,17 +7924,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499689</v>
+        <v>499634</v>
       </c>
       <c r="R55" t="n">
-        <v>7016946</v>
+        <v>7016955</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8153,27 +7958,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>20:07</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>20:07</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid hyggeskanten.</t>
+          <t>Rikligt med revlummer på en yta av minst 2 m2. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8182,6 +7977,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -8190,24 +7986,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk-fuktig och fuktig mark. Här finns olikåldriga träd och träd med socklar. Måttliga mängder med liggande, lutande och stående död ved.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8225,40 +8006,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124509973</v>
+        <v>118980813</v>
       </c>
       <c r="B56" t="n">
-        <v>57635</v>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8266,17 +8057,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499670</v>
+        <v>499374</v>
       </c>
       <c r="R56" t="n">
-        <v>7016915</v>
+        <v>7017134</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8300,27 +8091,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ca 6 meter på en något smalare gran vid hyggeskanten.</t>
+          <t>Spindelblomster med minst 2 st skott/stjälkar inom ca 1 m2 yta. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8329,6 +8110,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -8337,24 +8119,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På frisk och frisk-fuktig mark</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8372,40 +8139,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124510139</v>
+        <v>118981029</v>
       </c>
       <c r="B57" t="n">
-        <v>57635</v>
+        <v>99140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8413,14 +8190,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499682</v>
+        <v>499309</v>
       </c>
       <c r="R57" t="n">
-        <v>7016943</v>
+        <v>7017233</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8447,27 +8224,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>20:01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>20:01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs minst 6 meter på en gran med kådaflöden vid hyggeskanten.</t>
+          <t>Spindelblomster med minst 19 st skott/stjälkar inom ca 5 m2 yta. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8476,6 +8243,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -8484,24 +8252,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8519,40 +8272,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124509586</v>
+        <v>118981456</v>
       </c>
       <c r="B58" t="n">
-        <v>57635</v>
+        <v>99140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8560,17 +8323,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499669</v>
+        <v>499272</v>
       </c>
       <c r="R58" t="n">
-        <v>7016915</v>
+        <v>7017240</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8594,27 +8357,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>19:42</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>19:42</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en smal gran vid hyggeskanten. De färska ringhacken är troligen skapade 2025. I skogsbeståndet finns även avbarkade döda stående granar med potentiella färska födosökspår av tretåig hackspett.</t>
+          <t>Spindelblomster med minst 7 st skott/stjälkar inom ca 3 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8623,6 +8376,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8631,24 +8385,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8666,42 +8405,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124512397</v>
+        <v>118981652</v>
       </c>
       <c r="B59" t="n">
-        <v>57635</v>
+        <v>99140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8709,17 +8456,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Granskog söder om Fjäl (Fjäl 4:35), Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499437</v>
+        <v>499264</v>
       </c>
       <c r="R59" t="n">
-        <v>7016890</v>
+        <v>7017222</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8743,27 +8490,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>21:05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>21:05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, vid ca 3 meters höjd på en relativt grov gran med synliga kådaflöden. Kring fyndplatsen finns stående döda granar som indikerar högt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Spindelblomster med minst 7 st skott/stjälkar. Här finns även knärot. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8772,6 +8509,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8780,24 +8518,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn. Hyfsat gott om liggande och stående död ved. På fuktig och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8812,6 +8535,139 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>118982021</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Granskog söder om Fjäl (Fjäl 4:35), Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>499371</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7017042</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Spindelblomster med minst 16 st skott/stjälkar inom 1 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 26796-2024.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre skog med inslag av tall, björk och rönn på frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26796-2024 artfynd.xlsx
+++ b/artfynd/A 26796-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -816,6 +821,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120277408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -955,6 +965,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278324</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1099,6 +1114,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279007</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1241,6 +1261,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124508195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1385,6 +1410,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276314</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1521,6 +1551,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118980864</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1662,6 +1697,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118981709</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1798,6 +1838,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275394</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1938,6 +1983,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275534</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2079,6 +2129,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275779</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2215,6 +2270,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120277714</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2351,6 +2411,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120277809</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2487,6 +2552,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121192528</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2619,6 +2689,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124506970</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2766,6 +2841,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124509586</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2913,6 +2993,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124509973</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3060,6 +3145,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124510139</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3207,6 +3297,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124510250</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3356,6 +3451,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124512397</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3505,6 +3605,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124512733</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3631,6 +3736,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124508243</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3762,6 +3872,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124511642</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3890,6 +4005,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272977</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4018,6 +4138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278443</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4151,6 +4276,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118980671</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4284,6 +4414,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118981133</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4417,6 +4552,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118981571</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4550,6 +4690,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118981871</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4683,6 +4828,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272547</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4816,6 +4966,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272665</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4949,6 +5104,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273132</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5082,6 +5242,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273384</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5215,6 +5380,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273613</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5348,6 +5518,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273861</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5481,6 +5656,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275167</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5614,6 +5794,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275293</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5747,6 +5932,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276443</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5880,6 +6070,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276615</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6013,6 +6208,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276956</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6141,6 +6341,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120277439</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6274,6 +6479,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120277525</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6407,6 +6617,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120277899</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6540,6 +6755,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278049</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6673,6 +6893,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278994</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6806,6 +7031,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121192442</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6939,6 +7169,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121193255</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7072,6 +7307,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121193691</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7205,6 +7445,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121194234</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7338,6 +7583,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121194426</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7469,6 +7719,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124508038</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7600,6 +7855,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124508624</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7736,6 +7996,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124511068</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7874,6 +8139,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124511612</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8003,6 +8273,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120277582</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8136,6 +8411,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118980813</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8269,6 +8549,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118981029</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8402,6 +8687,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118981456</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8535,6 +8825,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118981652</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8668,8 +8963,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118982021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>